--- a/AAII_Financials/Quarterly/SNN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="92">
   <si>
     <t>SNN</t>
   </si>
@@ -656,328 +656,341 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45108</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44744</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44380</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44289</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44196</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44009</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43918</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43830</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43645</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43554</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43465</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43372</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43281</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43190</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43100</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43008</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>42917</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>42735</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>42644</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>42553</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2815000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2734000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2615000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2600000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2613000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2599000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1264000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2525000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2035000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1134000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2653000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2485000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1202000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2464000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1169000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2440000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1196000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2429000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1152000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2336000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2341000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1119000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2328000</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>894000</v>
+      </c>
+      <c r="E9" s="3">
         <v>836000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>767000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>773000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>737000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>806000</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="J9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K9" s="3">
         <v>750000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>646000</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N9" s="3">
         <v>690000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>648000</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3">
         <v>645000</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R9" s="3">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="3">
         <v>653000</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T9" s="3">
+      <c r="T9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U9" s="3">
         <v>645000</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V9" s="3">
+      <c r="V9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W9" s="3">
         <v>603000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>640000</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y9" s="3">
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z9" s="3">
         <v>632000</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1921000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1898000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1848000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1827000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1876000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1793000</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="J10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K10" s="3">
         <v>1775000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1389000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N10" s="3">
         <v>1963000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1837000</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3">
         <v>1819000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="3">
         <v>1787000</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T10" s="3">
+      <c r="T10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U10" s="3">
         <v>1784000</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V10" s="3">
+      <c r="V10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W10" s="3">
         <v>1733000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1701000</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y10" s="3">
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z10" s="3">
         <v>1696000</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1003,79 +1016,83 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>173000</v>
+      </c>
+      <c r="E12" s="3">
         <v>166000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>171000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>174000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>185000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>171000</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K12" s="3">
         <v>159000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>148000</v>
       </c>
-      <c r="L12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N12" s="3">
         <v>153000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>139000</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P12" s="3">
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="3">
         <v>130000</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R12" s="3">
+      <c r="R12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S12" s="3">
         <v>116000</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T12" s="3">
+      <c r="T12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U12" s="3">
         <v>116000</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V12" s="3">
+      <c r="V12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W12" s="3">
         <v>107000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>117000</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y12" s="3">
+      <c r="Y12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z12" s="3">
         <v>113000</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1145,150 +1162,159 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>155000</v>
+      </c>
+      <c r="E14" s="3">
         <v>40000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>91000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>93000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-37000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>133000</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3">
         <v>74000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>94000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>123000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>52000</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3">
         <v>56000</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="3">
         <v>78000</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="3">
         <v>-30000</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W14" s="3">
         <v>14000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-326000</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>105000</v>
+      </c>
+      <c r="E15" s="3">
         <v>102000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>64000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>105000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>150000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>87000</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="J15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K15" s="3">
         <v>151000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>83000</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M15" s="3">
+      <c r="M15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N15" s="3">
         <v>100000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>61000</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P15" s="3">
+      <c r="P15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="3">
         <v>56000</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R15" s="3">
+      <c r="R15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S15" s="3">
         <v>57000</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T15" s="3">
+      <c r="T15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U15" s="3">
         <v>127000</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V15" s="3">
+      <c r="V15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W15" s="3">
         <v>65000</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X15" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Y15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1311,150 +1337,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2665000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2459000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2407000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2358000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2184000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2360000</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="J17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K17" s="3">
         <v>2225000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2040000</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N17" s="3">
         <v>2257000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2066000</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="P17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="3">
         <v>1973000</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R17" s="3">
+      <c r="R17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S17" s="3">
         <v>2068000</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T17" s="3">
+      <c r="T17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U17" s="3">
         <v>1909000</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V17" s="3">
+      <c r="V17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W17" s="3">
         <v>1922000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1571000</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y17" s="3">
+      <c r="Y17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z17" s="3">
         <v>1971000</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>150000</v>
+      </c>
+      <c r="E18" s="3">
         <v>275000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>208000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>242000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>429000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>239000</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="J18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K18" s="3">
         <v>300000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5000</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N18" s="3">
         <v>396000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>419000</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="3">
         <v>491000</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S18" s="3">
         <v>372000</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U18" s="3">
         <v>520000</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W18" s="3">
         <v>414000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>770000</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z18" s="3">
         <v>357000</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1480,150 +1513,157 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-64000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-177000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-38000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-66000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-16000</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
         <v>-20000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-29000</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="3">
         <v>-9000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-6000</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-51000</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S20" s="3">
         <v>-31000</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U20" s="3">
         <v>-24000</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W20" s="3">
         <v>-3000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-35000</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-30000</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>465000</v>
+      </c>
+      <c r="E21" s="3">
         <v>508000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>339000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>513000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>636000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>517000</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="J21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K21" s="3">
         <v>842000</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N21" s="3">
         <v>641000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>661000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="3">
         <v>647000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="R21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S21" s="3">
         <v>569000</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U21" s="3">
         <v>724000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W21" s="3">
         <v>630000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>984000</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z21" s="3">
         <v>541000</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1654,15 +1694,15 @@
       <c r="L22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N22" s="3">
         <v>27000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>30000</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
@@ -1681,162 +1721,171 @@
       <c r="U22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W22" s="3">
         <v>28000</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>79000</v>
+      </c>
+      <c r="E23" s="3">
         <v>211000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>31000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>204000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>363000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>223000</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="J23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K23" s="3">
         <v>280000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-34000</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N23" s="3">
         <v>360000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>383000</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P23" s="3">
+      <c r="P23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q23" s="3">
         <v>440000</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R23" s="3">
+      <c r="R23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S23" s="3">
         <v>341000</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T23" s="3">
+      <c r="T23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U23" s="3">
         <v>496000</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V23" s="3">
+      <c r="V23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W23" s="3">
         <v>383000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>735000</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y23" s="3">
+      <c r="Y23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z23" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-12000</v>
+      </c>
+      <c r="E24" s="3">
         <v>39000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-15000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>27000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>44000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>18000</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="J24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K24" s="3">
         <v>-68000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-134000</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N24" s="3">
         <v>69000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>74000</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q24" s="3">
         <v>51000</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="R24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S24" s="3">
         <v>67000</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T24" s="3">
+      <c r="T24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U24" s="3">
         <v>21000</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V24" s="3">
+      <c r="V24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W24" s="3">
         <v>59000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>192000</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y24" s="3">
+      <c r="Y24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z24" s="3">
         <v>86000</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1906,150 +1955,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E26" s="3">
         <v>172000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>46000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>177000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>319000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>205000</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="J26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K26" s="3">
         <v>348000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>100000</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N26" s="3">
         <v>291000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>309000</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P26" s="3">
+      <c r="P26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q26" s="3">
         <v>389000</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R26" s="3">
+      <c r="R26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S26" s="3">
         <v>274000</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T26" s="3">
+      <c r="T26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U26" s="3">
         <v>475000</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V26" s="3">
+      <c r="V26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W26" s="3">
         <v>324000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>543000</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y26" s="3">
+      <c r="Y26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z26" s="3">
         <v>241000</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E27" s="3">
         <v>172000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>46000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>177000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>319000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>205000</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="J27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K27" s="3">
         <v>348000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>100000</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N27" s="3">
         <v>291000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>309000</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P27" s="3">
+      <c r="P27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="3">
         <v>389000</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R27" s="3">
+      <c r="R27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S27" s="3">
         <v>274000</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T27" s="3">
+      <c r="T27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U27" s="3">
         <v>475000</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V27" s="3">
+      <c r="V27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W27" s="3">
         <v>324000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>543000</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y27" s="3">
+      <c r="Y27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z27" s="3">
         <v>241000</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2119,8 +2177,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2154,17 +2215,17 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>5</v>
+      <c r="N29" s="3">
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>5</v>
+      <c r="P29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>5</v>
@@ -2172,12 +2233,12 @@
       <c r="S29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T29" s="3">
+      <c r="T29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U29" s="3">
         <v>-32000</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2190,8 +2251,11 @@
       <c r="Y29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2261,8 +2325,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2332,150 +2399,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E32" s="3">
         <v>64000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>177000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>38000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>66000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>16000</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
         <v>20000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>29000</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
         <v>9000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>6000</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="3">
         <v>51000</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S32" s="3">
         <v>31000</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="T32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U32" s="3">
         <v>24000</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W32" s="3">
         <v>3000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>35000</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z32" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E33" s="3">
         <v>172000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>46000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>177000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>319000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>205000</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="J33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K33" s="3">
         <v>348000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>100000</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N33" s="3">
         <v>291000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>309000</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P33" s="3">
+      <c r="P33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="3">
         <v>389000</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R33" s="3">
+      <c r="R33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S33" s="3">
         <v>274000</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T33" s="3">
+      <c r="T33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U33" s="3">
         <v>443000</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V33" s="3">
+      <c r="V33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W33" s="3">
         <v>324000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>543000</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y33" s="3">
+      <c r="Y33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z33" s="3">
         <v>241000</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2545,155 +2621,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E35" s="3">
         <v>172000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>46000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>177000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>319000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>205000</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="J35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K35" s="3">
         <v>348000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>100000</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N35" s="3">
         <v>291000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>309000</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P35" s="3">
+      <c r="P35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="3">
         <v>389000</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R35" s="3">
+      <c r="R35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S35" s="3">
         <v>274000</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T35" s="3">
+      <c r="T35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U35" s="3">
         <v>443000</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V35" s="3">
+      <c r="V35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W35" s="3">
         <v>324000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>543000</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y35" s="3">
+      <c r="Y35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z35" s="3">
         <v>241000</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45108</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44744</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44380</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44289</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44196</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44009</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43918</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43830</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43645</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43554</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43465</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43372</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43281</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43190</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43100</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43008</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>42917</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>42735</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>42644</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>42553</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2719,8 +2804,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2746,79 +2832,83 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>302000</v>
+      </c>
+      <c r="E41" s="3">
         <v>190000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>350000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>516000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1290000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1387000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1762000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>347000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>277000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>137000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>365000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>137000</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P41" s="3">
+      <c r="P41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q41" s="3">
         <v>365000</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R41" s="3">
+      <c r="R41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S41" s="3">
         <v>99000</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T41" s="3">
+      <c r="T41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U41" s="3">
         <v>169000</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V41" s="3">
+      <c r="V41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W41" s="3">
         <v>69000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>100000</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y41" s="3">
+      <c r="Y41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z41" s="3">
         <v>85000</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2888,150 +2978,159 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1333000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1277000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1301000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1253000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1290000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1305000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1211000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1231000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1328000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1280000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1317000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1280000</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P43" s="3">
+      <c r="P43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q43" s="3">
         <v>1317000</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R43" s="3">
+      <c r="R43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S43" s="3">
         <v>1205000</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T43" s="3">
+      <c r="T43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U43" s="3">
         <v>1258000</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V43" s="3">
+      <c r="V43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W43" s="3">
         <v>1212000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1185000</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y43" s="3">
+      <c r="Y43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z43" s="3">
         <v>1166000</v>
       </c>
     </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2395000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2411000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2205000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1990000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1844000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1750000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1691000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1721000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1614000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1532000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1395000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1532000</v>
       </c>
-      <c r="O44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P44" s="3">
+      <c r="P44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q44" s="3">
         <v>1395000</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R44" s="3">
+      <c r="R44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S44" s="3">
         <v>1352000</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T44" s="3">
+      <c r="T44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U44" s="3">
         <v>1304000</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V44" s="3">
+      <c r="V44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W44" s="3">
         <v>1298000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1244000</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y44" s="3">
+      <c r="Y44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z44" s="3">
         <v>1291000</v>
       </c>
     </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3092,301 +3191,316 @@
       <c r="V45" s="3">
         <v>0</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>5</v>
+      <c r="W45" s="3">
+        <v>0</v>
       </c>
       <c r="X45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Y45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z45" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4030000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3878000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3856000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3759000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4424000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4442000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4664000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3299000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3219000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2949000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3077000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2949000</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P46" s="3">
+      <c r="P46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q46" s="3">
         <v>3077000</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R46" s="3">
+      <c r="R46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S46" s="3">
         <v>2656000</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T46" s="3">
+      <c r="T46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U46" s="3">
         <v>2731000</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V46" s="3">
+      <c r="V46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W46" s="3">
         <v>2579000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2529000</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y46" s="3">
+      <c r="Y46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z46" s="3">
         <v>2552000</v>
       </c>
     </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E47" s="3">
         <v>35000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>58000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>195000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>198000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>146000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>117000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>106000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>110000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>109000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>139000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>109000</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q47" s="3">
         <v>139000</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R47" s="3">
+      <c r="R47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S47" s="3">
         <v>140000</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T47" s="3">
+      <c r="T47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U47" s="3">
         <v>139000</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V47" s="3">
+      <c r="V47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W47" s="3">
         <v>135000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>137000</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y47" s="3">
+      <c r="Y47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z47" s="3">
         <v>127000</v>
       </c>
     </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1470000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1421000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1455000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1460000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1513000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1453000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1449000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1353000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1323000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1226000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1062000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1226000</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P48" s="3">
+      <c r="P48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q48" s="3">
         <v>1062000</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R48" s="3">
+      <c r="R48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S48" s="3">
         <v>1056000</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T48" s="3">
+      <c r="T48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U48" s="3">
         <v>1049000</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V48" s="3">
+      <c r="V48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W48" s="3">
         <v>1032000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>982000</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y48" s="3">
+      <c r="Y48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z48" s="3">
         <v>946000</v>
       </c>
     </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4102000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4229000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4267000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4338000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4387000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4485000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4414000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4398000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4356000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4391000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3547000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4391000</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P49" s="3">
+      <c r="P49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q49" s="3">
         <v>3547000</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R49" s="3">
+      <c r="R49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S49" s="3">
         <v>3638000</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T49" s="3">
+      <c r="T49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U49" s="3">
         <v>3742000</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V49" s="3">
+      <c r="V49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W49" s="3">
         <v>3587000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3599000</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y49" s="3">
+      <c r="Y49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z49" s="3">
         <v>3762000</v>
       </c>
     </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3456,8 +3570,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3527,79 +3644,85 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>361000</v>
+      </c>
+      <c r="E52" s="3">
         <v>281000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>330000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>353000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>398000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>407000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>368000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>383000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>291000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>271000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>234000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>271000</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P52" s="3">
+      <c r="P52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q52" s="3">
         <v>234000</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R52" s="3">
+      <c r="R52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S52" s="3">
         <v>223000</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T52" s="3">
+      <c r="T52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U52" s="3">
         <v>205000</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V52" s="3">
+      <c r="V52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W52" s="3">
         <v>106000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>97000</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y52" s="3">
+      <c r="Y52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z52" s="3">
         <v>115000</v>
       </c>
     </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3669,79 +3792,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9987000</v>
+      </c>
+      <c r="E54" s="3">
         <v>9844000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9966000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10105000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10920000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10933000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11012000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>9539000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9299000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8946000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8059000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8946000</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P54" s="3">
+      <c r="P54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q54" s="3">
         <v>8059000</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R54" s="3">
+      <c r="R54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S54" s="3">
         <v>7713000</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T54" s="3">
+      <c r="T54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U54" s="3">
         <v>7866000</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V54" s="3">
+      <c r="V54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W54" s="3">
         <v>7439000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7344000</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y54" s="3">
+      <c r="Y54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z54" s="3">
         <v>7502000</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3767,8 +3896,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3794,434 +3924,453 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1055000</v>
+      </c>
+      <c r="E57" s="3">
         <v>955000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1098000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1013000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1096000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1046000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1022000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>875000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1046000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>906000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>957000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>906000</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P57" s="3">
+      <c r="P57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q57" s="3">
         <v>957000</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R57" s="3">
+      <c r="R57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S57" s="3">
         <v>831000</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T57" s="3">
+      <c r="T57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U57" s="3">
         <v>957000</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V57" s="3">
+      <c r="V57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W57" s="3">
         <v>792000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>884000</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z57" s="3">
         <v>842000</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>765000</v>
+      </c>
+      <c r="E58" s="3">
         <v>407000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>160000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>612000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>491000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>650000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>337000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>163000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>72000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>199000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>164000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>199000</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P58" s="3">
+      <c r="P58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q58" s="3">
         <v>164000</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R58" s="3">
+      <c r="R58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S58" s="3">
         <v>86000</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T58" s="3">
+      <c r="T58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U58" s="3">
         <v>27000</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V58" s="3">
+      <c r="V58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W58" s="3">
         <v>64000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>86000</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y58" s="3">
+      <c r="Y58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z58" s="3">
         <v>71000</v>
       </c>
     </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>451000</v>
+      </c>
+      <c r="E59" s="3">
         <v>405000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>457000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>492000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>544000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>424000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>329000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>478000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>446000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>369000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>344000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>369000</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P59" s="3">
+      <c r="P59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q59" s="3">
         <v>344000</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R59" s="3">
+      <c r="R59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S59" s="3">
         <v>330000</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T59" s="3">
+      <c r="T59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U59" s="3">
         <v>362000</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V59" s="3">
+      <c r="V59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W59" s="3">
         <v>329000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>378000</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y59" s="3">
+      <c r="Y59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z59" s="3">
         <v>432000</v>
       </c>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2271000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1767000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1715000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2117000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2131000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2120000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1688000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1516000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1564000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1474000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1465000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1474000</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P60" s="3">
+      <c r="P60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q60" s="3">
         <v>1465000</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R60" s="3">
+      <c r="R60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S60" s="3">
         <v>1247000</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T60" s="3">
+      <c r="T60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U60" s="3">
         <v>1346000</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V60" s="3">
+      <c r="V60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W60" s="3">
         <v>1185000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1348000</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y60" s="3">
+      <c r="Y60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z60" s="3">
         <v>1345000</v>
       </c>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2319000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2633000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2712000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2281000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2848000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2916000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3353000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2476000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1975000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1980000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1301000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1980000</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>1301000</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
         <v>1420000</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>1423000</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>1604000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1564000</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>1708000</v>
       </c>
     </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>180000</v>
+      </c>
+      <c r="E62" s="3">
         <v>211000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>280000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>312000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>373000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>566000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>692000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>587000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>619000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>540000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>419000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>540000</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q62" s="3">
         <v>419000</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R62" s="3">
+      <c r="R62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S62" s="3">
         <v>403000</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T62" s="3">
+      <c r="T62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U62" s="3">
         <v>453000</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V62" s="3">
+      <c r="V62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W62" s="3">
         <v>449000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>474000</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y62" s="3">
+      <c r="Y62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z62" s="3">
         <v>505000</v>
       </c>
     </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4291,8 +4440,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4362,8 +4514,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4433,79 +4588,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4770000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4611000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4707000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4710000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5352000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5602000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5733000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4579000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4158000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3994000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3185000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3994000</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P66" s="3">
+      <c r="P66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q66" s="3">
         <v>3185000</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R66" s="3">
+      <c r="R66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S66" s="3">
         <v>3070000</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T66" s="3">
+      <c r="T66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U66" s="3">
         <v>3222000</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V66" s="3">
+      <c r="V66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W66" s="3">
         <v>3238000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3386000</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y66" s="3">
+      <c r="Y66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z66" s="3">
         <v>3558000</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4531,8 +4692,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4602,8 +4764,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4673,8 +4838,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4744,8 +4912,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4815,79 +4986,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4521000</v>
+      </c>
+      <c r="E72" s="3">
         <v>4550000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4587000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4711000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4897000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4680000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4647000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4349000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4543000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4370000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4303000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4370000</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q72" s="3">
         <v>4303000</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R72" s="3">
+      <c r="R72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S72" s="3">
         <v>4092000</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T72" s="3">
+      <c r="T72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U72" s="3">
         <v>4118000</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V72" s="3">
+      <c r="V72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W72" s="3">
         <v>3680000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3610000</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z72" s="3">
         <v>3450000</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4957,8 +5134,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5028,8 +5208,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5099,79 +5282,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5217000</v>
+      </c>
+      <c r="E76" s="3">
         <v>5233000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5259000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5395000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5568000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5331000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5279000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4960000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5141000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4952000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4874000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4952000</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P76" s="3">
+      <c r="P76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q76" s="3">
         <v>4874000</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R76" s="3">
+      <c r="R76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S76" s="3">
         <v>4643000</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T76" s="3">
+      <c r="T76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U76" s="3">
         <v>4644000</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V76" s="3">
+      <c r="V76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W76" s="3">
         <v>4201000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3958000</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y76" s="3">
+      <c r="Y76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z76" s="3">
         <v>3944000</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5241,155 +5430,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45108</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44744</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44380</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44289</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44196</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44009</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43918</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43830</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43645</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43554</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43465</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43372</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43281</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43190</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43100</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43008</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>42917</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>42735</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>42644</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>42553</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E81" s="3">
         <v>172000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>46000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>177000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>319000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>205000</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="J81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K81" s="3">
         <v>348000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>100000</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N81" s="3">
         <v>291000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>309000</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P81" s="3">
+      <c r="P81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q81" s="3">
         <v>389000</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R81" s="3">
+      <c r="R81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S81" s="3">
         <v>274000</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T81" s="3">
+      <c r="T81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U81" s="3">
         <v>443000</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V81" s="3">
+      <c r="V81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W81" s="3">
         <v>324000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>543000</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y81" s="3">
+      <c r="Y81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z81" s="3">
         <v>241000</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5415,79 +5613,83 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>386000</v>
+      </c>
+      <c r="E83" s="3">
         <v>297000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>308000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>309000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>273000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>294000</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K83" s="3">
         <v>562000</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="3">
         <v>254000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>248000</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="P83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q83" s="3">
         <v>207000</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R83" s="3">
+      <c r="R83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S83" s="3">
         <v>228000</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T83" s="3">
+      <c r="T83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U83" s="3">
         <v>228000</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V83" s="3">
+      <c r="V83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W83" s="3">
         <v>219000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>249000</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y83" s="3">
+      <c r="Y83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z83" s="3">
         <v>214000</v>
       </c>
     </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5557,8 +5759,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5628,8 +5833,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5699,8 +5907,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5770,8 +5981,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5841,79 +6055,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>495000</v>
+      </c>
+      <c r="E89" s="3">
         <v>113000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>261000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>207000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>514000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>363000</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K89" s="3">
         <v>935000</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N89" s="3">
         <v>717000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>451000</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="P89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q89" s="3">
         <v>634000</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S89" s="3">
         <v>297000</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T89" s="3">
+      <c r="T89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U89" s="3">
         <v>739000</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V89" s="3">
+      <c r="V89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W89" s="3">
         <v>351000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>580000</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y89" s="3">
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z89" s="3">
         <v>269000</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5939,79 +6159,83 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-260000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-167000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-185000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-173000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-233000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-175000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-255000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-188000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-255000</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M91" s="3">
+      <c r="M91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N91" s="3">
         <v>-255000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-153000</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P91" s="3">
+      <c r="P91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-169000</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R91" s="3">
+      <c r="R91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S91" s="3">
         <v>-178000</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T91" s="3">
+      <c r="T91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U91" s="3">
         <v>-198000</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V91" s="3">
+      <c r="V91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W91" s="3">
         <v>-178000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-218000</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-174000</v>
       </c>
     </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6081,8 +6305,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6152,79 +6379,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-266000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-182000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-204000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-268000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-260000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-431000</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K94" s="3">
         <v>-606000</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3">
         <v>-286000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-965000</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="P94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-179000</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R94" s="3">
+      <c r="R94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S94" s="3">
         <v>-199000</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T94" s="3">
+      <c r="T94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U94" s="3">
         <v>-326000</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V94" s="3">
+      <c r="V94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W94" s="3">
         <v>-217000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>5000</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-388000</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6250,79 +6483,83 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-126000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-201000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-125000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-202000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-126000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-203000</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>-328000</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-126000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-192000</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-123000</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-198000</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-107000</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-162000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-109000</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-170000</v>
       </c>
     </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6392,8 +6629,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6463,8 +6703,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6534,217 +6777,229 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-114000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-86000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-222000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-704000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-343000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-302000</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K100" s="3">
         <v>1164000</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N100" s="3">
         <v>-296000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>303000</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="P100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-202000</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S100" s="3">
         <v>-169000</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="T100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U100" s="3">
         <v>-304000</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V100" s="3">
+      <c r="V100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W100" s="3">
         <v>-130000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-598000</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z100" s="3">
         <v>69000</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-6000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-3000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-8000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-5000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2000</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K101" s="3">
         <v>1000</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R101" s="3">
+      <c r="R101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S101" s="3">
         <v>-3000</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T101" s="3">
+      <c r="T101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U101" s="3">
         <v>2000</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V101" s="3">
+      <c r="V101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W101" s="3">
         <v>2000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2000</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y101" s="3">
+      <c r="Y101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>117000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-161000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-168000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-773000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-94000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-372000</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J102" s="3">
+      <c r="J102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K102" s="3">
         <v>1494000</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M102" s="3">
+      <c r="M102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N102" s="3">
         <v>135000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-211000</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P102" s="3">
+      <c r="P102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q102" s="3">
         <v>252000</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R102" s="3">
+      <c r="R102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S102" s="3">
         <v>-74000</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="T102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U102" s="3">
         <v>111000</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V102" s="3">
+      <c r="V102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W102" s="3">
         <v>6000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-15000</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-49000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SNN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="92">
   <si>
     <t>SNN</t>
   </si>
@@ -656,341 +656,354 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45108</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44744</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44561</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44380</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44289</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44196</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44009</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43918</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43830</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43645</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43554</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43465</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43372</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43281</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43190</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43100</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43008</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>42917</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>42735</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>42644</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>42553</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2827000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2815000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2734000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2615000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2600000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2613000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2599000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1264000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2525000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2035000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1134000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2653000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2485000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1202000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2464000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1169000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2440000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1196000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2429000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1152000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2336000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2341000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1119000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2328000</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>853000</v>
+      </c>
+      <c r="E9" s="3">
         <v>894000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>836000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>767000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>773000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>737000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>806000</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L9" s="3">
         <v>750000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>646000</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N9" s="3">
+      <c r="N9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O9" s="3">
         <v>690000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>648000</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3">
         <v>645000</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S9" s="3">
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T9" s="3">
         <v>653000</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U9" s="3">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V9" s="3">
         <v>645000</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W9" s="3">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X9" s="3">
         <v>603000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>640000</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z9" s="3">
+      <c r="Z9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA9" s="3">
         <v>632000</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1974000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1921000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1898000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1848000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1827000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1876000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1793000</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L10" s="3">
         <v>1775000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1389000</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O10" s="3">
         <v>1963000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1837000</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3">
         <v>1819000</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S10" s="3">
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T10" s="3">
         <v>1787000</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V10" s="3">
         <v>1784000</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X10" s="3">
         <v>1733000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1701000</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z10" s="3">
+      <c r="Z10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA10" s="3">
         <v>1696000</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1017,82 +1030,86 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>137000</v>
+      </c>
+      <c r="E12" s="3">
         <v>173000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>166000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>171000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>174000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>185000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>171000</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L12" s="3">
         <v>159000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>148000</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N12" s="3">
+      <c r="N12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O12" s="3">
         <v>153000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>139000</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R12" s="3">
         <v>130000</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S12" s="3">
+      <c r="S12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T12" s="3">
         <v>116000</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U12" s="3">
+      <c r="U12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V12" s="3">
         <v>116000</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W12" s="3">
+      <c r="W12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X12" s="3">
         <v>107000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>117000</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z12" s="3">
+      <c r="Z12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA12" s="3">
         <v>113000</v>
       </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1165,156 +1182,165 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>155000</v>
+        <v>62000</v>
       </c>
       <c r="E14" s="3">
-        <v>40000</v>
+        <v>156000</v>
       </c>
       <c r="F14" s="3">
-        <v>91000</v>
+        <v>29000</v>
       </c>
       <c r="G14" s="3">
-        <v>93000</v>
+        <v>84000</v>
       </c>
       <c r="H14" s="3">
-        <v>-37000</v>
+        <v>64000</v>
       </c>
       <c r="I14" s="3">
-        <v>133000</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K14" s="3">
+        <v>-44000</v>
+      </c>
+      <c r="J14" s="3">
+        <v>89000</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
         <v>74000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>94000</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="3">
         <v>123000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>52000</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
         <v>56000</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3">
         <v>78000</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="3">
         <v>-30000</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" s="3">
         <v>14000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-326000</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>87000</v>
+      </c>
+      <c r="E15" s="3">
         <v>105000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>102000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>64000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>105000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>150000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>87000</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K15" s="3">
+      <c r="K15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L15" s="3">
         <v>151000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>83000</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N15" s="3">
+      <c r="N15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O15" s="3">
         <v>100000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>61000</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15" s="3">
         <v>56000</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S15" s="3">
+      <c r="S15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T15" s="3">
         <v>57000</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V15" s="3">
         <v>127000</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W15" s="3">
+      <c r="W15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X15" s="3">
         <v>65000</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y15" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1338,156 +1364,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2499000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2665000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2459000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2407000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2358000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2184000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2360000</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L17" s="3">
         <v>2225000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2040000</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O17" s="3">
         <v>2257000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2066000</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" s="3">
         <v>1973000</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S17" s="3">
+      <c r="S17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T17" s="3">
         <v>2068000</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V17" s="3">
         <v>1909000</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W17" s="3">
+      <c r="W17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X17" s="3">
         <v>1922000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1571000</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z17" s="3">
+      <c r="Z17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA17" s="3">
         <v>1971000</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>328000</v>
+      </c>
+      <c r="E18" s="3">
         <v>150000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>275000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>208000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>242000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>429000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>239000</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L18" s="3">
         <v>300000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5000</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O18" s="3">
         <v>396000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>419000</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" s="3">
         <v>491000</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T18" s="3">
         <v>372000</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V18" s="3">
         <v>520000</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X18" s="3">
         <v>414000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>770000</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="Z18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA18" s="3">
         <v>357000</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1514,179 +1547,186 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-71000</v>
+        <v>-5000</v>
       </c>
       <c r="E20" s="3">
-        <v>-64000</v>
+        <v>-1000</v>
       </c>
       <c r="F20" s="3">
-        <v>-177000</v>
+        <v>-2000</v>
       </c>
       <c r="G20" s="3">
-        <v>-38000</v>
+        <v>-132000</v>
       </c>
       <c r="H20" s="3">
-        <v>-66000</v>
+        <v>-3000</v>
       </c>
       <c r="I20" s="3">
-        <v>-16000</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K20" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="J20" s="3">
+        <v>26000</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>-20000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-29000</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O20" s="3">
         <v>-9000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-6000</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>-51000</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T20" s="3">
         <v>-31000</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V20" s="3">
         <v>-24000</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X20" s="3">
         <v>-3000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-35000</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="Z20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-30000</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>465000</v>
+        <v>596000</v>
       </c>
       <c r="E21" s="3">
-        <v>508000</v>
+        <v>535000</v>
       </c>
       <c r="F21" s="3">
-        <v>339000</v>
+        <v>570000</v>
       </c>
       <c r="G21" s="3">
-        <v>513000</v>
+        <v>384000</v>
       </c>
       <c r="H21" s="3">
-        <v>636000</v>
+        <v>548000</v>
       </c>
       <c r="I21" s="3">
-        <v>517000</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K21" s="3">
+        <v>674000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>559000</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L21" s="3">
         <v>842000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O21" s="3">
         <v>641000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>661000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3">
         <v>647000</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="3">
         <v>569000</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V21" s="3">
         <v>724000</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X21" s="3">
         <v>630000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>984000</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA21" s="3">
         <v>541000</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>5</v>
+      <c r="D22" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>70000</v>
+      </c>
+      <c r="F22" s="3">
+        <v>62000</v>
+      </c>
+      <c r="G22" s="3">
+        <v>45000</v>
+      </c>
+      <c r="H22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="I22" s="3">
+        <v>38000</v>
+      </c>
+      <c r="J22" s="3">
+        <v>42000</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>5</v>
@@ -1697,15 +1737,15 @@
       <c r="M22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O22" s="3">
         <v>27000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>30000</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>5</v>
       </c>
@@ -1724,168 +1764,177 @@
       <c r="V22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X22" s="3">
         <v>28000</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>253000</v>
+      </c>
+      <c r="E23" s="3">
         <v>79000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>211000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>31000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>204000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>363000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>223000</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L23" s="3">
         <v>280000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-34000</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O23" s="3">
         <v>360000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>383000</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R23" s="3">
         <v>440000</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S23" s="3">
+      <c r="S23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T23" s="3">
         <v>341000</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U23" s="3">
+      <c r="U23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V23" s="3">
         <v>496000</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W23" s="3">
+      <c r="W23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X23" s="3">
         <v>383000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>735000</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z23" s="3">
+      <c r="Z23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA23" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-12000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>39000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-15000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>27000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>44000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>18000</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L24" s="3">
         <v>-68000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-134000</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="N24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O24" s="3">
         <v>69000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>74000</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R24" s="3">
         <v>51000</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S24" s="3">
+      <c r="S24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T24" s="3">
         <v>67000</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U24" s="3">
+      <c r="U24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V24" s="3">
         <v>21000</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W24" s="3">
+      <c r="W24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X24" s="3">
         <v>59000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>192000</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z24" s="3">
+      <c r="Z24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA24" s="3">
         <v>86000</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1958,156 +2007,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>214000</v>
+      </c>
+      <c r="E26" s="3">
         <v>91000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>172000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>46000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>177000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>319000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>205000</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L26" s="3">
         <v>348000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>100000</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O26" s="3">
         <v>291000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>309000</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R26" s="3">
         <v>389000</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S26" s="3">
+      <c r="S26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T26" s="3">
         <v>274000</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V26" s="3">
         <v>475000</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W26" s="3">
+      <c r="W26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X26" s="3">
         <v>324000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>543000</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z26" s="3">
+      <c r="Z26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA26" s="3">
         <v>241000</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>214000</v>
+      </c>
+      <c r="E27" s="3">
         <v>91000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>172000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>46000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>177000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>319000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>205000</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L27" s="3">
         <v>348000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>100000</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O27" s="3">
         <v>291000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>309000</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R27" s="3">
         <v>389000</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S27" s="3">
+      <c r="S27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T27" s="3">
         <v>274000</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V27" s="3">
         <v>475000</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W27" s="3">
+      <c r="W27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X27" s="3">
         <v>324000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>543000</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z27" s="3">
+      <c r="Z27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA27" s="3">
         <v>241000</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2180,8 +2238,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2218,17 +2279,17 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>5</v>
+      <c r="O29" s="3">
+        <v>0</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>5</v>
+      <c r="Q29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>5</v>
@@ -2236,12 +2297,12 @@
       <c r="T29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U29" s="3">
+      <c r="U29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V29" s="3">
         <v>-32000</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2254,8 +2315,11 @@
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2328,8 +2392,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2402,156 +2469,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>71000</v>
+        <v>5000</v>
       </c>
       <c r="E32" s="3">
-        <v>64000</v>
+        <v>1000</v>
       </c>
       <c r="F32" s="3">
-        <v>177000</v>
+        <v>2000</v>
       </c>
       <c r="G32" s="3">
-        <v>38000</v>
+        <v>132000</v>
       </c>
       <c r="H32" s="3">
-        <v>66000</v>
+        <v>3000</v>
       </c>
       <c r="I32" s="3">
-        <v>16000</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K32" s="3">
+        <v>28000</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>20000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>29000</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O32" s="3">
         <v>9000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>6000</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>51000</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T32" s="3">
         <v>31000</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V32" s="3">
         <v>24000</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X32" s="3">
         <v>3000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>35000</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="Z32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA32" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>214000</v>
+      </c>
+      <c r="E33" s="3">
         <v>91000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>172000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>46000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>177000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>319000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>205000</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L33" s="3">
         <v>348000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>100000</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O33" s="3">
         <v>291000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>309000</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R33" s="3">
         <v>389000</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S33" s="3">
+      <c r="S33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T33" s="3">
         <v>274000</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V33" s="3">
         <v>443000</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W33" s="3">
+      <c r="W33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X33" s="3">
         <v>324000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>543000</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z33" s="3">
+      <c r="Z33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA33" s="3">
         <v>241000</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2624,161 +2700,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>214000</v>
+      </c>
+      <c r="E35" s="3">
         <v>91000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>172000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>46000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>177000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>319000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>205000</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L35" s="3">
         <v>348000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>100000</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O35" s="3">
         <v>291000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>309000</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R35" s="3">
         <v>389000</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S35" s="3">
+      <c r="S35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T35" s="3">
         <v>274000</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V35" s="3">
         <v>443000</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W35" s="3">
+      <c r="W35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X35" s="3">
         <v>324000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>543000</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z35" s="3">
+      <c r="Z35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA35" s="3">
         <v>241000</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45108</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44744</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44561</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44380</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44289</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44196</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44009</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43918</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43830</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43645</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43554</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43465</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43372</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43281</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43190</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43100</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43008</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>42917</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>42735</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>42644</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>42553</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2805,8 +2890,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2833,82 +2919,86 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>568000</v>
+      </c>
+      <c r="E41" s="3">
         <v>302000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>190000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>350000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>516000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1290000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1387000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1762000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>347000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>277000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>137000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>365000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>137000</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q41" s="3">
+      <c r="Q41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R41" s="3">
         <v>365000</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S41" s="3">
+      <c r="S41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T41" s="3">
         <v>99000</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U41" s="3">
+      <c r="U41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V41" s="3">
         <v>169000</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W41" s="3">
+      <c r="W41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X41" s="3">
         <v>69000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>100000</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z41" s="3">
+      <c r="Z41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA41" s="3">
         <v>85000</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2981,156 +3071,165 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1399000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1333000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1277000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1301000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1253000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1290000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1305000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1211000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1231000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1328000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1280000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1317000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1280000</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q43" s="3">
+      <c r="Q43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R43" s="3">
         <v>1317000</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S43" s="3">
+      <c r="S43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T43" s="3">
         <v>1205000</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U43" s="3">
+      <c r="U43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V43" s="3">
         <v>1258000</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W43" s="3">
+      <c r="W43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X43" s="3">
         <v>1212000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1185000</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z43" s="3">
+      <c r="Z43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA43" s="3">
         <v>1166000</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2491000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2395000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2411000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2205000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1990000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1844000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1750000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1691000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1721000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1614000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1532000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1395000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1532000</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q44" s="3">
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R44" s="3">
         <v>1395000</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S44" s="3">
+      <c r="S44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T44" s="3">
         <v>1352000</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U44" s="3">
+      <c r="U44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V44" s="3">
         <v>1304000</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W44" s="3">
+      <c r="W44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X44" s="3">
         <v>1298000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1244000</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z44" s="3">
+      <c r="Z44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA44" s="3">
         <v>1291000</v>
       </c>
     </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3194,91 +3293,97 @@
       <c r="W45" s="3">
         <v>0</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>5</v>
+      <c r="X45" s="3">
+        <v>0</v>
       </c>
       <c r="Y45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="Z45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA45" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4458000</v>
+      </c>
+      <c r="E46" s="3">
         <v>4030000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3878000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3856000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3759000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4424000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4442000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4664000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3299000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3219000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2949000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3077000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2949000</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q46" s="3">
+      <c r="Q46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R46" s="3">
         <v>3077000</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S46" s="3">
+      <c r="S46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T46" s="3">
         <v>2656000</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U46" s="3">
+      <c r="U46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V46" s="3">
         <v>2731000</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W46" s="3">
+      <c r="W46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X46" s="3">
         <v>2579000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2529000</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z46" s="3">
+      <c r="Z46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA46" s="3">
         <v>2552000</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3286,221 +3391,230 @@
         <v>24000</v>
       </c>
       <c r="E47" s="3">
+        <v>24000</v>
+      </c>
+      <c r="F47" s="3">
         <v>35000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>58000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>195000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>198000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>146000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>117000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>106000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>110000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>109000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>139000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>109000</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R47" s="3">
         <v>139000</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S47" s="3">
+      <c r="S47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T47" s="3">
         <v>140000</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U47" s="3">
+      <c r="U47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V47" s="3">
         <v>139000</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W47" s="3">
+      <c r="W47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X47" s="3">
         <v>135000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>137000</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z47" s="3">
+      <c r="Z47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA47" s="3">
         <v>127000</v>
       </c>
     </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1441000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1470000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1421000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1455000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1460000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1513000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1453000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1449000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1353000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1323000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1226000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1062000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1226000</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q48" s="3">
+      <c r="Q48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R48" s="3">
         <v>1062000</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S48" s="3">
+      <c r="S48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T48" s="3">
         <v>1056000</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U48" s="3">
+      <c r="U48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V48" s="3">
         <v>1049000</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W48" s="3">
+      <c r="W48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X48" s="3">
         <v>1032000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>982000</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z48" s="3">
+      <c r="Z48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA48" s="3">
         <v>946000</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4216000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4102000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4229000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4267000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4338000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4387000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4485000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4414000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4398000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4356000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4391000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3547000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4391000</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q49" s="3">
+      <c r="Q49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R49" s="3">
         <v>3547000</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S49" s="3">
+      <c r="S49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T49" s="3">
         <v>3638000</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U49" s="3">
+      <c r="U49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V49" s="3">
         <v>3742000</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W49" s="3">
+      <c r="W49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X49" s="3">
         <v>3587000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3599000</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z49" s="3">
+      <c r="Z49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA49" s="3">
         <v>3762000</v>
       </c>
     </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3573,8 +3687,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3647,82 +3764,88 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>403000</v>
+      </c>
+      <c r="E52" s="3">
         <v>361000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>281000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>330000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>353000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>398000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>407000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>368000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>383000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>291000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>271000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>234000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>271000</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q52" s="3">
+      <c r="Q52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R52" s="3">
         <v>234000</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S52" s="3">
+      <c r="S52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T52" s="3">
         <v>223000</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U52" s="3">
+      <c r="U52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V52" s="3">
         <v>205000</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W52" s="3">
+      <c r="W52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X52" s="3">
         <v>106000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>97000</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z52" s="3">
+      <c r="Z52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA52" s="3">
         <v>115000</v>
       </c>
     </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3795,82 +3918,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10542000</v>
+      </c>
+      <c r="E54" s="3">
         <v>9987000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9844000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9966000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10105000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10920000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10933000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11012000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9539000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9299000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8946000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8059000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8946000</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q54" s="3">
+      <c r="Q54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R54" s="3">
         <v>8059000</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S54" s="3">
+      <c r="S54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T54" s="3">
         <v>7713000</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U54" s="3">
+      <c r="U54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V54" s="3">
         <v>7866000</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W54" s="3">
+      <c r="W54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X54" s="3">
         <v>7439000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>7344000</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z54" s="3">
+      <c r="Z54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA54" s="3">
         <v>7502000</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3897,8 +4026,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3925,452 +4055,471 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1024000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1055000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>955000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1098000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1013000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1096000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1046000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1022000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>875000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1046000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>906000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>957000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>906000</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q57" s="3">
+      <c r="Q57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R57" s="3">
         <v>957000</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S57" s="3">
+      <c r="S57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T57" s="3">
         <v>831000</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U57" s="3">
+      <c r="U57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V57" s="3">
         <v>957000</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W57" s="3">
+      <c r="W57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X57" s="3">
         <v>792000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>884000</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z57" s="3">
+      <c r="Z57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA57" s="3">
         <v>842000</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>380000</v>
+      </c>
+      <c r="E58" s="3">
         <v>765000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>407000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>160000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>612000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>491000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>650000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>337000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>163000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>72000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>199000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>164000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>199000</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q58" s="3">
+      <c r="Q58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R58" s="3">
         <v>164000</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S58" s="3">
+      <c r="S58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T58" s="3">
         <v>86000</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U58" s="3">
+      <c r="U58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V58" s="3">
         <v>27000</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W58" s="3">
+      <c r="W58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X58" s="3">
         <v>64000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>86000</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z58" s="3">
+      <c r="Z58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA58" s="3">
         <v>71000</v>
       </c>
     </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>373000</v>
+      </c>
+      <c r="E59" s="3">
         <v>451000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>405000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>457000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>492000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>544000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>424000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>329000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>478000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>446000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>369000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>344000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>369000</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R59" s="3">
         <v>344000</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S59" s="3">
+      <c r="S59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T59" s="3">
         <v>330000</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V59" s="3">
         <v>362000</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W59" s="3">
+      <c r="W59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X59" s="3">
         <v>329000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>378000</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z59" s="3">
+      <c r="Z59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA59" s="3">
         <v>432000</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1777000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2271000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1767000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1715000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2117000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2131000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2120000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1688000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1516000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1564000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1474000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1465000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1474000</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q60" s="3">
+      <c r="Q60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R60" s="3">
         <v>1465000</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S60" s="3">
+      <c r="S60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T60" s="3">
         <v>1247000</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U60" s="3">
+      <c r="U60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V60" s="3">
         <v>1346000</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W60" s="3">
+      <c r="W60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X60" s="3">
         <v>1185000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1348000</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z60" s="3">
+      <c r="Z60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA60" s="3">
         <v>1345000</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3275000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2319000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2633000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2712000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2281000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2848000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2916000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3353000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2476000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1975000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1980000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1301000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1980000</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>1301000</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>1420000</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>1423000</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>1604000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1564000</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3">
         <v>1708000</v>
       </c>
     </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>285000</v>
+      </c>
+      <c r="E62" s="3">
         <v>180000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>211000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>280000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>312000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>373000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>566000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>692000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>587000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>619000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>540000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>419000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>540000</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q62" s="3">
+      <c r="Q62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R62" s="3">
         <v>419000</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S62" s="3">
+      <c r="S62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T62" s="3">
         <v>403000</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U62" s="3">
+      <c r="U62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V62" s="3">
         <v>453000</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W62" s="3">
+      <c r="W62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X62" s="3">
         <v>449000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>474000</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z62" s="3">
+      <c r="Z62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA62" s="3">
         <v>505000</v>
       </c>
     </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4443,8 +4592,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4517,8 +4669,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4591,82 +4746,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5337000</v>
+      </c>
+      <c r="E66" s="3">
         <v>4770000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4611000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4707000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4710000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5352000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5602000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5733000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4579000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4158000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3994000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3185000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3994000</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q66" s="3">
+      <c r="Q66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R66" s="3">
         <v>3185000</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S66" s="3">
+      <c r="S66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T66" s="3">
         <v>3070000</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U66" s="3">
+      <c r="U66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V66" s="3">
         <v>3222000</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W66" s="3">
+      <c r="W66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X66" s="3">
         <v>3238000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3386000</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z66" s="3">
+      <c r="Z66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA66" s="3">
         <v>3558000</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4693,8 +4854,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4767,8 +4929,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4841,8 +5006,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4915,8 +5083,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4989,82 +5160,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4497000</v>
+      </c>
+      <c r="E72" s="3">
         <v>4521000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4550000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4587000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4711000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4897000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4680000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>4647000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4349000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4543000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4370000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4303000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4370000</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R72" s="3">
         <v>4303000</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T72" s="3">
         <v>4092000</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V72" s="3">
         <v>4118000</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X72" s="3">
         <v>3680000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>3610000</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z72" s="3">
+      <c r="Z72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA72" s="3">
         <v>3450000</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5137,8 +5314,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5211,8 +5391,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5285,82 +5468,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5205000</v>
+      </c>
+      <c r="E76" s="3">
         <v>5217000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5233000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5259000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5395000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5568000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5331000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5279000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4960000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5141000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4952000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4874000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4952000</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q76" s="3">
+      <c r="Q76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R76" s="3">
         <v>4874000</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S76" s="3">
+      <c r="S76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T76" s="3">
         <v>4643000</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U76" s="3">
+      <c r="U76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V76" s="3">
         <v>4644000</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W76" s="3">
+      <c r="W76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X76" s="3">
         <v>4201000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3958000</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z76" s="3">
+      <c r="Z76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA76" s="3">
         <v>3944000</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5433,161 +5622,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45108</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44744</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44561</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44380</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44289</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44196</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44009</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43918</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43830</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43645</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43554</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43465</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43372</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43281</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43190</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43100</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43008</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>42917</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>42735</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>42644</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>42553</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>214000</v>
+      </c>
+      <c r="E81" s="3">
         <v>91000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>172000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>46000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>177000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>319000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>205000</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L81" s="3">
         <v>348000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>100000</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O81" s="3">
         <v>291000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>309000</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R81" s="3">
         <v>389000</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S81" s="3">
+      <c r="S81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T81" s="3">
         <v>274000</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V81" s="3">
         <v>443000</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W81" s="3">
+      <c r="W81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X81" s="3">
         <v>324000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>543000</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z81" s="3">
+      <c r="Z81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA81" s="3">
         <v>241000</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5614,82 +5812,86 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>273000</v>
+      </c>
+      <c r="E83" s="3">
         <v>386000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>297000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>308000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>309000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>273000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>294000</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L83" s="3">
         <v>562000</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N83" s="3">
+      <c r="N83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O83" s="3">
         <v>254000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>248000</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
         <v>207000</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3">
         <v>228000</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V83" s="3">
         <v>228000</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X83" s="3">
         <v>219000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>249000</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z83" s="3">
+      <c r="Z83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA83" s="3">
         <v>214000</v>
       </c>
     </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5762,8 +5964,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5836,8 +6041,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5910,8 +6118,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5984,8 +6195,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6058,82 +6272,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>238000</v>
+      </c>
+      <c r="E89" s="3">
         <v>495000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>113000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>261000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>207000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>514000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>363000</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L89" s="3">
         <v>935000</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N89" s="3">
+      <c r="N89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O89" s="3">
         <v>717000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>451000</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3">
         <v>634000</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3">
         <v>297000</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V89" s="3">
         <v>739000</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X89" s="3">
         <v>351000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>580000</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z89" s="3">
+      <c r="Z89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA89" s="3">
         <v>269000</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6160,82 +6380,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-172000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-260000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-167000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-185000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-173000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-233000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-175000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-255000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-188000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-255000</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N91" s="3">
+      <c r="N91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O91" s="3">
         <v>-255000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-153000</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R91" s="3">
         <v>-169000</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S91" s="3">
+      <c r="S91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T91" s="3">
         <v>-178000</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U91" s="3">
+      <c r="U91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V91" s="3">
         <v>-198000</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X91" s="3">
         <v>-178000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-218000</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z91" s="3">
+      <c r="Z91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-174000</v>
       </c>
     </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6308,8 +6532,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6382,82 +6609,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-360000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-266000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-182000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-204000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-268000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-260000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-431000</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K94" s="3">
+      <c r="K94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L94" s="3">
         <v>-606000</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N94" s="3">
+      <c r="N94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O94" s="3">
         <v>-286000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-965000</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
         <v>-179000</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3">
         <v>-199000</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V94" s="3">
         <v>-326000</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X94" s="3">
         <v>-217000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>5000</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z94" s="3">
+      <c r="Z94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA94" s="3">
         <v>-388000</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6484,82 +6717,86 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-202000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-126000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-201000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-125000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-202000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-126000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-203000</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-328000</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-126000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-192000</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-123000</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-198000</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-107000</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-162000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-109000</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-170000</v>
       </c>
     </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6632,8 +6869,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6706,8 +6946,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6780,226 +7023,238 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>372000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-114000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-86000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-222000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-704000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-343000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-302000</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L100" s="3">
         <v>1164000</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N100" s="3">
+      <c r="N100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O100" s="3">
         <v>-296000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>303000</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
         <v>-202000</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3">
         <v>-169000</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V100" s="3">
         <v>-304000</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X100" s="3">
         <v>-130000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-598000</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="Z100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA100" s="3">
         <v>69000</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E101" s="3">
         <v>2000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-6000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-3000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-8000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2000</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L101" s="3">
         <v>1000</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="3">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
         <v>-1000</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3">
         <v>-3000</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U101" s="3">
+      <c r="U101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V101" s="3">
         <v>2000</v>
       </c>
-      <c r="V101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W101" s="3">
+      <c r="W101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X101" s="3">
         <v>2000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z101" s="3">
+      <c r="Z101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>245000</v>
+      </c>
+      <c r="E102" s="3">
         <v>117000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-161000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-168000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-773000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-94000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-372000</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K102" s="3">
+      <c r="K102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L102" s="3">
         <v>1494000</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N102" s="3">
+      <c r="N102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O102" s="3">
         <v>135000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-211000</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3">
         <v>252000</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3">
         <v>-74000</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V102" s="3">
         <v>111000</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X102" s="3">
         <v>6000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-15000</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z102" s="3">
+      <c r="Z102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA102" s="3">
         <v>-49000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SNN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="92">
   <si>
     <t>SNN</t>
   </si>
@@ -663,12 +663,11 @@
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -703,22 +702,22 @@
         <v>45472</v>
       </c>
       <c r="E7" s="2">
+        <v>45380</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45108</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
+        <v>45017</v>
+      </c>
+      <c r="J7" s="2">
         <v>44926</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44744</v>
-      </c>
-      <c r="I7" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44380</v>
       </c>
       <c r="K7" s="2">
         <v>44289</v>
@@ -777,25 +776,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>2827000</v>
+        <v>1413500</v>
       </c>
       <c r="E8" s="3">
-        <v>2815000</v>
+        <v>1413500</v>
       </c>
       <c r="F8" s="3">
-        <v>2734000</v>
+        <v>1407500</v>
       </c>
       <c r="G8" s="3">
-        <v>2615000</v>
+        <v>1407500</v>
       </c>
       <c r="H8" s="3">
-        <v>2600000</v>
+        <v>1367000</v>
       </c>
       <c r="I8" s="3">
-        <v>2613000</v>
+        <v>1367000</v>
       </c>
       <c r="J8" s="3">
-        <v>2599000</v>
+        <v>1307500</v>
       </c>
       <c r="K8" s="3">
         <v>1264000</v>
@@ -854,25 +853,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>853000</v>
+        <v>426500</v>
       </c>
       <c r="E9" s="3">
-        <v>894000</v>
+        <v>426500</v>
       </c>
       <c r="F9" s="3">
-        <v>836000</v>
+        <v>410500</v>
       </c>
       <c r="G9" s="3">
-        <v>767000</v>
+        <v>410500</v>
       </c>
       <c r="H9" s="3">
-        <v>773000</v>
+        <v>418000</v>
       </c>
       <c r="I9" s="3">
-        <v>737000</v>
+        <v>418000</v>
       </c>
       <c r="J9" s="3">
-        <v>806000</v>
+        <v>373500</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
@@ -931,25 +930,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>1974000</v>
+        <v>987000</v>
       </c>
       <c r="E10" s="3">
-        <v>1921000</v>
+        <v>987000</v>
       </c>
       <c r="F10" s="3">
-        <v>1898000</v>
+        <v>997000</v>
       </c>
       <c r="G10" s="3">
-        <v>1848000</v>
+        <v>997000</v>
       </c>
       <c r="H10" s="3">
-        <v>1827000</v>
+        <v>949000</v>
       </c>
       <c r="I10" s="3">
-        <v>1876000</v>
+        <v>949000</v>
       </c>
       <c r="J10" s="3">
-        <v>1793000</v>
+        <v>934000</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -1037,25 +1036,25 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>137000</v>
+        <v>68500</v>
       </c>
       <c r="E12" s="3">
-        <v>173000</v>
+        <v>68500</v>
       </c>
       <c r="F12" s="3">
-        <v>166000</v>
+        <v>77000</v>
       </c>
       <c r="G12" s="3">
-        <v>171000</v>
+        <v>77000</v>
       </c>
       <c r="H12" s="3">
-        <v>174000</v>
+        <v>83000</v>
       </c>
       <c r="I12" s="3">
-        <v>185000</v>
+        <v>83000</v>
       </c>
       <c r="J12" s="3">
-        <v>171000</v>
+        <v>80500</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>5</v>
@@ -1190,26 +1189,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>62000</v>
-      </c>
-      <c r="E14" s="3">
-        <v>156000</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F14" s="3">
-        <v>29000</v>
+        <v>132000</v>
       </c>
       <c r="G14" s="3">
-        <v>84000</v>
-      </c>
-      <c r="H14" s="3">
-        <v>64000</v>
-      </c>
-      <c r="I14" s="3">
-        <v>-44000</v>
+        <v>132000</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J14" s="3">
-        <v>89000</v>
+        <v>112000</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
@@ -1268,25 +1267,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>87000</v>
+        <v>96000</v>
       </c>
       <c r="E15" s="3">
-        <v>105000</v>
+        <v>96000</v>
       </c>
       <c r="F15" s="3">
-        <v>102000</v>
+        <v>69000</v>
       </c>
       <c r="G15" s="3">
-        <v>64000</v>
+        <v>69000</v>
       </c>
       <c r="H15" s="3">
-        <v>105000</v>
+        <v>143000</v>
       </c>
       <c r="I15" s="3">
-        <v>150000</v>
+        <v>143000</v>
       </c>
       <c r="J15" s="3">
-        <v>87000</v>
+        <v>70000</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>5</v>
@@ -1371,25 +1370,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2499000</v>
+        <v>1249500</v>
       </c>
       <c r="E17" s="3">
-        <v>2665000</v>
+        <v>1249500</v>
       </c>
       <c r="F17" s="3">
-        <v>2459000</v>
+        <v>1204000</v>
       </c>
       <c r="G17" s="3">
-        <v>2407000</v>
+        <v>1204000</v>
       </c>
       <c r="H17" s="3">
-        <v>2358000</v>
+        <v>1229500</v>
       </c>
       <c r="I17" s="3">
-        <v>2184000</v>
+        <v>1229500</v>
       </c>
       <c r="J17" s="3">
-        <v>2360000</v>
+        <v>1096000</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>5</v>
@@ -1448,25 +1447,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>328000</v>
+        <v>164000</v>
       </c>
       <c r="E18" s="3">
-        <v>150000</v>
+        <v>164000</v>
       </c>
       <c r="F18" s="3">
-        <v>275000</v>
+        <v>203500</v>
       </c>
       <c r="G18" s="3">
-        <v>208000</v>
+        <v>203500</v>
       </c>
       <c r="H18" s="3">
-        <v>242000</v>
+        <v>137500</v>
       </c>
       <c r="I18" s="3">
-        <v>429000</v>
+        <v>137500</v>
       </c>
       <c r="J18" s="3">
-        <v>239000</v>
+        <v>211500</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>5</v>
@@ -1554,25 +1553,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-5000</v>
+        <v>7000</v>
       </c>
       <c r="E20" s="3">
-        <v>-1000</v>
+        <v>7000</v>
       </c>
       <c r="F20" s="3">
-        <v>-2000</v>
+        <v>5000</v>
       </c>
       <c r="G20" s="3">
-        <v>-132000</v>
+        <v>5000</v>
       </c>
       <c r="H20" s="3">
-        <v>-3000</v>
+        <v>10000</v>
       </c>
       <c r="I20" s="3">
-        <v>-28000</v>
+        <v>10000</v>
       </c>
       <c r="J20" s="3">
-        <v>26000</v>
+        <v>67000</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>5</v>
@@ -1631,25 +1630,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>596000</v>
+        <v>253000</v>
       </c>
       <c r="E21" s="3">
-        <v>535000</v>
+        <v>253000</v>
       </c>
       <c r="F21" s="3">
-        <v>570000</v>
+        <v>267500</v>
       </c>
       <c r="G21" s="3">
-        <v>384000</v>
+        <v>267500</v>
       </c>
       <c r="H21" s="3">
-        <v>548000</v>
+        <v>270500</v>
       </c>
       <c r="I21" s="3">
-        <v>674000</v>
+        <v>270500</v>
       </c>
       <c r="J21" s="3">
-        <v>559000</v>
+        <v>214500</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>5</v>
@@ -1708,25 +1707,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>70000</v>
+        <v>35000</v>
       </c>
       <c r="E22" s="3">
-        <v>70000</v>
+        <v>35000</v>
       </c>
       <c r="F22" s="3">
-        <v>62000</v>
+        <v>35000</v>
       </c>
       <c r="G22" s="3">
-        <v>45000</v>
+        <v>35000</v>
       </c>
       <c r="H22" s="3">
-        <v>35000</v>
+        <v>31000</v>
       </c>
       <c r="I22" s="3">
-        <v>38000</v>
+        <v>31000</v>
       </c>
       <c r="J22" s="3">
-        <v>42000</v>
+        <v>22500</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>5</v>
@@ -1785,25 +1784,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>253000</v>
+        <v>126500</v>
       </c>
       <c r="E23" s="3">
-        <v>79000</v>
+        <v>126500</v>
       </c>
       <c r="F23" s="3">
-        <v>211000</v>
+        <v>39500</v>
       </c>
       <c r="G23" s="3">
-        <v>31000</v>
+        <v>39500</v>
       </c>
       <c r="H23" s="3">
-        <v>204000</v>
+        <v>105500</v>
       </c>
       <c r="I23" s="3">
-        <v>363000</v>
+        <v>105500</v>
       </c>
       <c r="J23" s="3">
-        <v>223000</v>
+        <v>15500</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>5</v>
@@ -1862,25 +1861,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>39000</v>
+        <v>19500</v>
       </c>
       <c r="E24" s="3">
-        <v>-12000</v>
+        <v>19500</v>
       </c>
       <c r="F24" s="3">
-        <v>39000</v>
+        <v>-6000</v>
       </c>
       <c r="G24" s="3">
-        <v>-15000</v>
+        <v>-6000</v>
       </c>
       <c r="H24" s="3">
-        <v>27000</v>
+        <v>19500</v>
       </c>
       <c r="I24" s="3">
-        <v>44000</v>
+        <v>19500</v>
       </c>
       <c r="J24" s="3">
-        <v>18000</v>
+        <v>-7500</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>5</v>
@@ -2016,25 +2015,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>214000</v>
+        <v>107000</v>
       </c>
       <c r="E26" s="3">
-        <v>91000</v>
+        <v>107000</v>
       </c>
       <c r="F26" s="3">
-        <v>172000</v>
+        <v>45500</v>
       </c>
       <c r="G26" s="3">
-        <v>46000</v>
+        <v>45500</v>
       </c>
       <c r="H26" s="3">
-        <v>177000</v>
+        <v>86000</v>
       </c>
       <c r="I26" s="3">
-        <v>319000</v>
+        <v>86000</v>
       </c>
       <c r="J26" s="3">
-        <v>205000</v>
+        <v>23000</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>5</v>
@@ -2093,25 +2092,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>214000</v>
+        <v>107000</v>
       </c>
       <c r="E27" s="3">
-        <v>91000</v>
+        <v>107000</v>
       </c>
       <c r="F27" s="3">
-        <v>172000</v>
+        <v>45500</v>
       </c>
       <c r="G27" s="3">
-        <v>46000</v>
+        <v>45500</v>
       </c>
       <c r="H27" s="3">
-        <v>177000</v>
+        <v>86000</v>
       </c>
       <c r="I27" s="3">
-        <v>319000</v>
+        <v>86000</v>
       </c>
       <c r="J27" s="3">
-        <v>205000</v>
+        <v>23000</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>5</v>
@@ -2478,25 +2477,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>5000</v>
+        <v>-7000</v>
       </c>
       <c r="E32" s="3">
-        <v>1000</v>
+        <v>-7000</v>
       </c>
       <c r="F32" s="3">
-        <v>2000</v>
+        <v>-5000</v>
       </c>
       <c r="G32" s="3">
-        <v>132000</v>
+        <v>-5000</v>
       </c>
       <c r="H32" s="3">
-        <v>3000</v>
+        <v>-10000</v>
       </c>
       <c r="I32" s="3">
-        <v>28000</v>
+        <v>-10000</v>
       </c>
       <c r="J32" s="3">
-        <v>-26000</v>
+        <v>-67000</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>5</v>
@@ -2555,25 +2554,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>214000</v>
+        <v>107000</v>
       </c>
       <c r="E33" s="3">
-        <v>91000</v>
+        <v>107000</v>
       </c>
       <c r="F33" s="3">
-        <v>172000</v>
+        <v>45500</v>
       </c>
       <c r="G33" s="3">
-        <v>46000</v>
+        <v>45500</v>
       </c>
       <c r="H33" s="3">
-        <v>177000</v>
+        <v>86000</v>
       </c>
       <c r="I33" s="3">
-        <v>319000</v>
+        <v>86000</v>
       </c>
       <c r="J33" s="3">
-        <v>205000</v>
+        <v>23000</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>5</v>
@@ -2709,25 +2708,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>214000</v>
+        <v>107000</v>
       </c>
       <c r="E35" s="3">
-        <v>91000</v>
+        <v>107000</v>
       </c>
       <c r="F35" s="3">
-        <v>172000</v>
+        <v>45500</v>
       </c>
       <c r="G35" s="3">
-        <v>46000</v>
+        <v>45500</v>
       </c>
       <c r="H35" s="3">
-        <v>177000</v>
+        <v>86000</v>
       </c>
       <c r="I35" s="3">
-        <v>319000</v>
+        <v>86000</v>
       </c>
       <c r="J35" s="3">
-        <v>205000</v>
+        <v>23000</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>5</v>
@@ -2794,22 +2793,22 @@
         <v>45472</v>
       </c>
       <c r="E38" s="2">
+        <v>45380</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45108</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
+        <v>45017</v>
+      </c>
+      <c r="J38" s="2">
         <v>44926</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44744</v>
-      </c>
-      <c r="I38" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44380</v>
       </c>
       <c r="K38" s="2">
         <v>44289</v>
@@ -2929,22 +2928,22 @@
         <v>568000</v>
       </c>
       <c r="E41" s="3">
+        <v>568000</v>
+      </c>
+      <c r="F41" s="3">
         <v>302000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
+        <v>302000</v>
+      </c>
+      <c r="H41" s="3">
         <v>190000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
+        <v>190000</v>
+      </c>
+      <c r="J41" s="3">
         <v>350000</v>
-      </c>
-      <c r="H41" s="3">
-        <v>516000</v>
-      </c>
-      <c r="I41" s="3">
-        <v>1290000</v>
-      </c>
-      <c r="J41" s="3">
-        <v>1387000</v>
       </c>
       <c r="K41" s="3">
         <v>1762000</v>
@@ -3083,22 +3082,22 @@
         <v>1399000</v>
       </c>
       <c r="E43" s="3">
-        <v>1333000</v>
+        <v>1399000</v>
       </c>
       <c r="F43" s="3">
+        <v>1214000</v>
+      </c>
+      <c r="G43" s="3">
+        <v>1214000</v>
+      </c>
+      <c r="H43" s="3">
         <v>1277000</v>
       </c>
-      <c r="G43" s="3">
-        <v>1301000</v>
-      </c>
-      <c r="H43" s="3">
-        <v>1253000</v>
-      </c>
       <c r="I43" s="3">
-        <v>1290000</v>
+        <v>1277000</v>
       </c>
       <c r="J43" s="3">
-        <v>1305000</v>
+        <v>1178000</v>
       </c>
       <c r="K43" s="3">
         <v>1211000</v>
@@ -3160,22 +3159,22 @@
         <v>2491000</v>
       </c>
       <c r="E44" s="3">
+        <v>2491000</v>
+      </c>
+      <c r="F44" s="3">
         <v>2395000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
+        <v>2395000</v>
+      </c>
+      <c r="H44" s="3">
         <v>2411000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
+        <v>2411000</v>
+      </c>
+      <c r="J44" s="3">
         <v>2205000</v>
-      </c>
-      <c r="H44" s="3">
-        <v>1990000</v>
-      </c>
-      <c r="I44" s="3">
-        <v>1844000</v>
-      </c>
-      <c r="J44" s="3">
-        <v>1750000</v>
       </c>
       <c r="K44" s="3">
         <v>1691000</v>
@@ -3233,26 +3232,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
+        <v>27000</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>47000</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -3314,22 +3313,22 @@
         <v>4458000</v>
       </c>
       <c r="E46" s="3">
+        <v>4458000</v>
+      </c>
+      <c r="F46" s="3">
         <v>4030000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
+        <v>4030000</v>
+      </c>
+      <c r="H46" s="3">
         <v>3878000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
+        <v>3878000</v>
+      </c>
+      <c r="J46" s="3">
         <v>3856000</v>
-      </c>
-      <c r="H46" s="3">
-        <v>3759000</v>
-      </c>
-      <c r="I46" s="3">
-        <v>4424000</v>
-      </c>
-      <c r="J46" s="3">
-        <v>4442000</v>
       </c>
       <c r="K46" s="3">
         <v>4664000</v>
@@ -3394,19 +3393,19 @@
         <v>24000</v>
       </c>
       <c r="F47" s="3">
+        <v>24000</v>
+      </c>
+      <c r="G47" s="3">
+        <v>24000</v>
+      </c>
+      <c r="H47" s="3">
         <v>35000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
+        <v>35000</v>
+      </c>
+      <c r="J47" s="3">
         <v>58000</v>
-      </c>
-      <c r="H47" s="3">
-        <v>195000</v>
-      </c>
-      <c r="I47" s="3">
-        <v>198000</v>
-      </c>
-      <c r="J47" s="3">
-        <v>146000</v>
       </c>
       <c r="K47" s="3">
         <v>117000</v>
@@ -3468,22 +3467,22 @@
         <v>1441000</v>
       </c>
       <c r="E48" s="3">
+        <v>1441000</v>
+      </c>
+      <c r="F48" s="3">
         <v>1470000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
+        <v>1470000</v>
+      </c>
+      <c r="H48" s="3">
         <v>1421000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
+        <v>1421000</v>
+      </c>
+      <c r="J48" s="3">
         <v>1455000</v>
-      </c>
-      <c r="H48" s="3">
-        <v>1460000</v>
-      </c>
-      <c r="I48" s="3">
-        <v>1513000</v>
-      </c>
-      <c r="J48" s="3">
-        <v>1453000</v>
       </c>
       <c r="K48" s="3">
         <v>1449000</v>
@@ -3545,22 +3544,22 @@
         <v>4216000</v>
       </c>
       <c r="E49" s="3">
+        <v>4216000</v>
+      </c>
+      <c r="F49" s="3">
         <v>4102000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
+        <v>4102000</v>
+      </c>
+      <c r="H49" s="3">
         <v>4229000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
+        <v>4229000</v>
+      </c>
+      <c r="J49" s="3">
         <v>4267000</v>
-      </c>
-      <c r="H49" s="3">
-        <v>4338000</v>
-      </c>
-      <c r="I49" s="3">
-        <v>4387000</v>
-      </c>
-      <c r="J49" s="3">
-        <v>4485000</v>
       </c>
       <c r="K49" s="3">
         <v>4414000</v>
@@ -3773,25 +3772,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>403000</v>
+        <v>84000</v>
       </c>
       <c r="E52" s="3">
-        <v>361000</v>
+        <v>84000</v>
       </c>
       <c r="F52" s="3">
-        <v>281000</v>
+        <v>87000</v>
       </c>
       <c r="G52" s="3">
-        <v>330000</v>
+        <v>87000</v>
       </c>
       <c r="H52" s="3">
-        <v>353000</v>
+        <v>93000</v>
       </c>
       <c r="I52" s="3">
-        <v>398000</v>
+        <v>93000</v>
       </c>
       <c r="J52" s="3">
-        <v>407000</v>
+        <v>153000</v>
       </c>
       <c r="K52" s="3">
         <v>368000</v>
@@ -3930,22 +3929,22 @@
         <v>10542000</v>
       </c>
       <c r="E54" s="3">
+        <v>10542000</v>
+      </c>
+      <c r="F54" s="3">
         <v>9987000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
+        <v>9987000</v>
+      </c>
+      <c r="H54" s="3">
         <v>9844000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
+        <v>9844000</v>
+      </c>
+      <c r="J54" s="3">
         <v>9966000</v>
-      </c>
-      <c r="H54" s="3">
-        <v>10105000</v>
-      </c>
-      <c r="I54" s="3">
-        <v>10920000</v>
-      </c>
-      <c r="J54" s="3">
-        <v>10933000</v>
       </c>
       <c r="K54" s="3">
         <v>11012000</v>
@@ -4065,22 +4064,22 @@
         <v>1024000</v>
       </c>
       <c r="E57" s="3">
-        <v>1055000</v>
+        <v>1024000</v>
       </c>
       <c r="F57" s="3">
+        <v>1016000</v>
+      </c>
+      <c r="G57" s="3">
+        <v>1016000</v>
+      </c>
+      <c r="H57" s="3">
         <v>955000</v>
       </c>
-      <c r="G57" s="3">
-        <v>1098000</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1013000</v>
-      </c>
       <c r="I57" s="3">
-        <v>1096000</v>
+        <v>955000</v>
       </c>
       <c r="J57" s="3">
-        <v>1046000</v>
+        <v>1029000</v>
       </c>
       <c r="K57" s="3">
         <v>1022000</v>
@@ -4142,22 +4141,22 @@
         <v>380000</v>
       </c>
       <c r="E58" s="3">
+        <v>380000</v>
+      </c>
+      <c r="F58" s="3">
         <v>765000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
+        <v>765000</v>
+      </c>
+      <c r="H58" s="3">
         <v>407000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
+        <v>407000</v>
+      </c>
+      <c r="J58" s="3">
         <v>160000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>612000</v>
-      </c>
-      <c r="I58" s="3">
-        <v>491000</v>
-      </c>
-      <c r="J58" s="3">
-        <v>650000</v>
       </c>
       <c r="K58" s="3">
         <v>337000</v>
@@ -4219,22 +4218,22 @@
         <v>373000</v>
       </c>
       <c r="E59" s="3">
-        <v>451000</v>
+        <v>373000</v>
       </c>
       <c r="F59" s="3">
+        <v>490000</v>
+      </c>
+      <c r="G59" s="3">
+        <v>490000</v>
+      </c>
+      <c r="H59" s="3">
         <v>405000</v>
       </c>
-      <c r="G59" s="3">
-        <v>457000</v>
-      </c>
-      <c r="H59" s="3">
-        <v>492000</v>
-      </c>
       <c r="I59" s="3">
-        <v>544000</v>
+        <v>405000</v>
       </c>
       <c r="J59" s="3">
-        <v>424000</v>
+        <v>526000</v>
       </c>
       <c r="K59" s="3">
         <v>329000</v>
@@ -4296,22 +4295,22 @@
         <v>1777000</v>
       </c>
       <c r="E60" s="3">
+        <v>1777000</v>
+      </c>
+      <c r="F60" s="3">
         <v>2271000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
+        <v>2271000</v>
+      </c>
+      <c r="H60" s="3">
         <v>1767000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
+        <v>1767000</v>
+      </c>
+      <c r="J60" s="3">
         <v>1715000</v>
-      </c>
-      <c r="H60" s="3">
-        <v>2117000</v>
-      </c>
-      <c r="I60" s="3">
-        <v>2131000</v>
-      </c>
-      <c r="J60" s="3">
-        <v>2120000</v>
       </c>
       <c r="K60" s="3">
         <v>1688000</v>
@@ -4373,22 +4372,22 @@
         <v>3275000</v>
       </c>
       <c r="E61" s="3">
+        <v>3275000</v>
+      </c>
+      <c r="F61" s="3">
         <v>2319000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
+        <v>2319000</v>
+      </c>
+      <c r="H61" s="3">
         <v>2633000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
+        <v>2633000</v>
+      </c>
+      <c r="J61" s="3">
         <v>2712000</v>
-      </c>
-      <c r="H61" s="3">
-        <v>2281000</v>
-      </c>
-      <c r="I61" s="3">
-        <v>2848000</v>
-      </c>
-      <c r="J61" s="3">
-        <v>2916000</v>
       </c>
       <c r="K61" s="3">
         <v>3353000</v>
@@ -4447,25 +4446,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>285000</v>
+        <v>167000</v>
       </c>
       <c r="E62" s="3">
-        <v>180000</v>
+        <v>167000</v>
       </c>
       <c r="F62" s="3">
-        <v>211000</v>
+        <v>83000</v>
       </c>
       <c r="G62" s="3">
-        <v>280000</v>
+        <v>83000</v>
       </c>
       <c r="H62" s="3">
-        <v>312000</v>
+        <v>137000</v>
       </c>
       <c r="I62" s="3">
-        <v>373000</v>
+        <v>137000</v>
       </c>
       <c r="J62" s="3">
-        <v>566000</v>
+        <v>174000</v>
       </c>
       <c r="K62" s="3">
         <v>692000</v>
@@ -4758,22 +4757,22 @@
         <v>5337000</v>
       </c>
       <c r="E66" s="3">
+        <v>5337000</v>
+      </c>
+      <c r="F66" s="3">
         <v>4770000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
+        <v>4770000</v>
+      </c>
+      <c r="H66" s="3">
         <v>4611000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
+        <v>4611000</v>
+      </c>
+      <c r="J66" s="3">
         <v>4707000</v>
-      </c>
-      <c r="H66" s="3">
-        <v>4710000</v>
-      </c>
-      <c r="I66" s="3">
-        <v>5352000</v>
-      </c>
-      <c r="J66" s="3">
-        <v>5602000</v>
       </c>
       <c r="K66" s="3">
         <v>5733000</v>
@@ -5169,25 +5168,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>4497000</v>
+        <v>4934000</v>
       </c>
       <c r="E72" s="3">
-        <v>4521000</v>
+        <v>4934000</v>
       </c>
       <c r="F72" s="3">
-        <v>4550000</v>
+        <v>4906000</v>
       </c>
       <c r="G72" s="3">
-        <v>4587000</v>
+        <v>4906000</v>
       </c>
       <c r="H72" s="3">
-        <v>4711000</v>
+        <v>4963000</v>
       </c>
       <c r="I72" s="3">
-        <v>4897000</v>
+        <v>4963000</v>
       </c>
       <c r="J72" s="3">
-        <v>4680000</v>
+        <v>5026000</v>
       </c>
       <c r="K72" s="3">
         <v>4647000</v>
@@ -5480,22 +5479,22 @@
         <v>5205000</v>
       </c>
       <c r="E76" s="3">
+        <v>5205000</v>
+      </c>
+      <c r="F76" s="3">
         <v>5217000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
+        <v>5217000</v>
+      </c>
+      <c r="H76" s="3">
         <v>5233000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
+        <v>5233000</v>
+      </c>
+      <c r="J76" s="3">
         <v>5259000</v>
-      </c>
-      <c r="H76" s="3">
-        <v>5395000</v>
-      </c>
-      <c r="I76" s="3">
-        <v>5568000</v>
-      </c>
-      <c r="J76" s="3">
-        <v>5331000</v>
       </c>
       <c r="K76" s="3">
         <v>5279000</v>
@@ -5639,22 +5638,22 @@
         <v>45472</v>
       </c>
       <c r="E80" s="2">
+        <v>45380</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45108</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
+        <v>45017</v>
+      </c>
+      <c r="J80" s="2">
         <v>44926</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44744</v>
-      </c>
-      <c r="I80" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44380</v>
       </c>
       <c r="K80" s="2">
         <v>44289</v>
@@ -5713,25 +5712,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>214000</v>
+        <v>107000</v>
       </c>
       <c r="E81" s="3">
-        <v>91000</v>
+        <v>107000</v>
       </c>
       <c r="F81" s="3">
-        <v>172000</v>
+        <v>45500</v>
       </c>
       <c r="G81" s="3">
-        <v>46000</v>
+        <v>45500</v>
       </c>
       <c r="H81" s="3">
-        <v>177000</v>
+        <v>86000</v>
       </c>
       <c r="I81" s="3">
-        <v>319000</v>
+        <v>86000</v>
       </c>
       <c r="J81" s="3">
-        <v>205000</v>
+        <v>23000</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>5</v>
@@ -5819,25 +5818,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>273000</v>
+        <v>92000</v>
       </c>
       <c r="E83" s="3">
-        <v>386000</v>
+        <v>92000</v>
       </c>
       <c r="F83" s="3">
-        <v>297000</v>
+        <v>57500</v>
       </c>
       <c r="G83" s="3">
-        <v>308000</v>
+        <v>57500</v>
       </c>
       <c r="H83" s="3">
-        <v>309000</v>
+        <v>102000</v>
       </c>
       <c r="I83" s="3">
-        <v>273000</v>
+        <v>102000</v>
       </c>
       <c r="J83" s="3">
-        <v>294000</v>
+        <v>59000</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>5</v>
@@ -6281,25 +6280,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>238000</v>
+        <v>119000</v>
       </c>
       <c r="E89" s="3">
-        <v>495000</v>
+        <v>119000</v>
       </c>
       <c r="F89" s="3">
-        <v>113000</v>
+        <v>247500</v>
       </c>
       <c r="G89" s="3">
-        <v>261000</v>
+        <v>247500</v>
       </c>
       <c r="H89" s="3">
-        <v>207000</v>
+        <v>56500</v>
       </c>
       <c r="I89" s="3">
-        <v>514000</v>
+        <v>56500</v>
       </c>
       <c r="J89" s="3">
-        <v>363000</v>
+        <v>130500</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>5</v>
@@ -6387,25 +6386,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-172000</v>
+        <v>-86000</v>
       </c>
       <c r="E91" s="3">
-        <v>-260000</v>
+        <v>-86000</v>
       </c>
       <c r="F91" s="3">
-        <v>-167000</v>
+        <v>-130000</v>
       </c>
       <c r="G91" s="3">
-        <v>-185000</v>
+        <v>-130000</v>
       </c>
       <c r="H91" s="3">
-        <v>-173000</v>
+        <v>-83500</v>
       </c>
       <c r="I91" s="3">
-        <v>-233000</v>
+        <v>-83500</v>
       </c>
       <c r="J91" s="3">
-        <v>-175000</v>
+        <v>-92500</v>
       </c>
       <c r="K91" s="3">
         <v>-255000</v>
@@ -6618,25 +6617,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-360000</v>
+        <v>-180000</v>
       </c>
       <c r="E94" s="3">
-        <v>-266000</v>
+        <v>-180000</v>
       </c>
       <c r="F94" s="3">
-        <v>-182000</v>
+        <v>-133000</v>
       </c>
       <c r="G94" s="3">
-        <v>-204000</v>
+        <v>-133000</v>
       </c>
       <c r="H94" s="3">
-        <v>-268000</v>
+        <v>-91000</v>
       </c>
       <c r="I94" s="3">
-        <v>-260000</v>
+        <v>-91000</v>
       </c>
       <c r="J94" s="3">
-        <v>-431000</v>
+        <v>-102000</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>5</v>
@@ -6724,25 +6723,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-202000</v>
+        <v>101000</v>
       </c>
       <c r="E96" s="3">
-        <v>-126000</v>
+        <v>101000</v>
       </c>
       <c r="F96" s="3">
-        <v>-201000</v>
+        <v>63000</v>
       </c>
       <c r="G96" s="3">
-        <v>-125000</v>
+        <v>63000</v>
       </c>
       <c r="H96" s="3">
-        <v>-202000</v>
+        <v>100500</v>
       </c>
       <c r="I96" s="3">
-        <v>-126000</v>
+        <v>100500</v>
       </c>
       <c r="J96" s="3">
-        <v>-203000</v>
+        <v>62500</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -7032,25 +7031,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>372000</v>
+        <v>186000</v>
       </c>
       <c r="E100" s="3">
-        <v>-114000</v>
+        <v>186000</v>
       </c>
       <c r="F100" s="3">
-        <v>-86000</v>
+        <v>-57000</v>
       </c>
       <c r="G100" s="3">
-        <v>-222000</v>
+        <v>-57000</v>
       </c>
       <c r="H100" s="3">
-        <v>-704000</v>
+        <v>-43000</v>
       </c>
       <c r="I100" s="3">
-        <v>-343000</v>
+        <v>-43000</v>
       </c>
       <c r="J100" s="3">
-        <v>-302000</v>
+        <v>-111000</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>5</v>
@@ -7109,25 +7108,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-5000</v>
+        <v>-3000</v>
       </c>
       <c r="E101" s="3">
-        <v>2000</v>
+        <v>-3000</v>
       </c>
       <c r="F101" s="3">
-        <v>-6000</v>
+        <v>-1500</v>
       </c>
       <c r="G101" s="3">
-        <v>-3000</v>
+        <v>-1500</v>
       </c>
       <c r="H101" s="3">
-        <v>-8000</v>
+        <v>-4000</v>
       </c>
       <c r="I101" s="3">
-        <v>-5000</v>
+        <v>-4000</v>
       </c>
       <c r="J101" s="3">
-        <v>-2000</v>
+        <v>-2500</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>5</v>
@@ -7186,25 +7185,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>245000</v>
+        <v>122500</v>
       </c>
       <c r="E102" s="3">
-        <v>117000</v>
+        <v>122500</v>
       </c>
       <c r="F102" s="3">
-        <v>-161000</v>
+        <v>58500</v>
       </c>
       <c r="G102" s="3">
-        <v>-168000</v>
+        <v>58500</v>
       </c>
       <c r="H102" s="3">
-        <v>-773000</v>
+        <v>-80500</v>
       </c>
       <c r="I102" s="3">
-        <v>-94000</v>
+        <v>-80500</v>
       </c>
       <c r="J102" s="3">
-        <v>-372000</v>
+        <v>-84000</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>5</v>

--- a/AAII_Financials/Quarterly/SNN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNN_QTR_FIN.xlsx
@@ -656,353 +656,378 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45472</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45380</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45108</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45017</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44289</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44196</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44009</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43918</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43830</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43645</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43554</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43465</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43372</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43281</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43190</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43100</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43008</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42917</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42735</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42644</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42553</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1491500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1491500</v>
+      </c>
+      <c r="F8" s="3">
         <v>1413500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1413500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1407500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1407500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1367000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1367000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1307500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1264000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>2525000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>2035000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1134000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>2653000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>2485000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1202000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>2464000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1169000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>2440000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1196000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>2429000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1152000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>2336000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>2341000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>1119000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>2328000</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>439000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>439000</v>
+      </c>
+      <c r="F9" s="3">
         <v>426500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>426500</v>
       </c>
-      <c r="F9" s="3">
-        <v>410500</v>
-      </c>
-      <c r="G9" s="3">
-        <v>410500</v>
-      </c>
       <c r="H9" s="3">
+        <v>409000</v>
+      </c>
+      <c r="I9" s="3">
+        <v>409000</v>
+      </c>
+      <c r="J9" s="3">
         <v>418000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>418000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>373500</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N9" s="3">
         <v>750000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>646000</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3">
         <v>690000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>648000</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T9" s="3">
         <v>645000</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V9" s="3">
         <v>653000</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X9" s="3">
         <v>645000</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z9" s="3">
         <v>603000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>640000</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC9" s="3">
         <v>632000</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1052500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1052500</v>
+      </c>
+      <c r="F10" s="3">
         <v>987000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>987000</v>
       </c>
-      <c r="F10" s="3">
-        <v>997000</v>
-      </c>
-      <c r="G10" s="3">
-        <v>997000</v>
-      </c>
       <c r="H10" s="3">
+        <v>998500</v>
+      </c>
+      <c r="I10" s="3">
+        <v>998500</v>
+      </c>
+      <c r="J10" s="3">
         <v>949000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>949000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>934000</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N10" s="3">
         <v>1775000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>1389000</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3">
         <v>1963000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1837000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T10" s="3">
         <v>1819000</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V10" s="3">
         <v>1787000</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X10" s="3">
         <v>1784000</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z10" s="3">
         <v>1733000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>1701000</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC10" s="3">
         <v>1696000</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1030,61 +1055,63 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>76000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>76000</v>
+      </c>
+      <c r="F12" s="3">
         <v>68500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>68500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>77000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>77000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>83000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>83000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>80500</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N12" s="3">
         <v>159000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>148000</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="3">
         <v>153000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>139000</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T12" s="3">
         <v>130000</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T12" s="3">
-        <v>116000</v>
       </c>
       <c r="U12" s="3" t="s">
         <v>5</v>
@@ -1096,19 +1123,25 @@
         <v>5</v>
       </c>
       <c r="X12" s="3">
+        <v>116000</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z12" s="3">
         <v>107000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="AA12" s="3">
         <v>117000</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC12" s="3">
         <v>113000</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1184,162 +1217,180 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3">
-        <v>132000</v>
-      </c>
-      <c r="G14" s="3">
-        <v>132000</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="D14" s="3">
+        <v>116500</v>
+      </c>
+      <c r="E14" s="3">
+        <v>116500</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
+        <v>158500</v>
+      </c>
+      <c r="I14" s="3">
+        <v>158500</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
         <v>112000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>74000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>94000</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3">
         <v>123000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>52000</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3">
         <v>56000</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="3">
         <v>78000</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" s="3">
         <v>-30000</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z14" s="3">
         <v>14000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>-326000</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>128500</v>
+      </c>
+      <c r="E15" s="3">
+        <v>128500</v>
+      </c>
+      <c r="F15" s="3">
         <v>96000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>96000</v>
       </c>
-      <c r="F15" s="3">
-        <v>69000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>69000</v>
-      </c>
       <c r="H15" s="3">
+        <v>74500</v>
+      </c>
+      <c r="I15" s="3">
+        <v>74500</v>
+      </c>
+      <c r="J15" s="3">
         <v>143000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>143000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>70000</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N15" s="3">
         <v>151000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>83000</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="3">
         <v>100000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>61000</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T15" s="3">
         <v>56000</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V15" s="3">
         <v>57000</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X15" s="3">
         <v>127000</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z15" s="3">
         <v>65000</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1364,162 +1415,176 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1212500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1212500</v>
+      </c>
+      <c r="F17" s="3">
         <v>1249500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1249500</v>
       </c>
-      <c r="F17" s="3">
-        <v>1204000</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1204000</v>
-      </c>
       <c r="H17" s="3">
+        <v>1174500</v>
+      </c>
+      <c r="I17" s="3">
+        <v>1174500</v>
+      </c>
+      <c r="J17" s="3">
         <v>1229500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1229500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1096000</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N17" s="3">
         <v>2225000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2040000</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="3">
         <v>2257000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>2066000</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T17" s="3">
         <v>1973000</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V17" s="3">
         <v>2068000</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X17" s="3">
         <v>1909000</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z17" s="3">
         <v>1922000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>1571000</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC17" s="3">
         <v>1971000</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>279000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>279000</v>
+      </c>
+      <c r="F18" s="3">
         <v>164000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>164000</v>
       </c>
-      <c r="F18" s="3">
-        <v>203500</v>
-      </c>
-      <c r="G18" s="3">
-        <v>203500</v>
-      </c>
       <c r="H18" s="3">
+        <v>233000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>233000</v>
+      </c>
+      <c r="J18" s="3">
         <v>137500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>137500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>211500</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N18" s="3">
         <v>300000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-5000</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="3">
         <v>396000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>419000</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T18" s="3">
         <v>491000</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V18" s="3">
         <v>372000</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X18" s="3">
         <v>520000</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z18" s="3">
         <v>414000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>770000</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC18" s="3">
         <v>357000</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1547,170 +1612,184 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F20" s="3">
         <v>7000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>7000</v>
       </c>
-      <c r="F20" s="3">
-        <v>5000</v>
-      </c>
-      <c r="G20" s="3">
-        <v>5000</v>
-      </c>
       <c r="H20" s="3">
+        <v>8000</v>
+      </c>
+      <c r="I20" s="3">
+        <v>8000</v>
+      </c>
+      <c r="J20" s="3">
         <v>10000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>10000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>67000</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="3">
         <v>-20000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-29000</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-9000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T20" s="3">
         <v>-51000</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V20" s="3">
         <v>-31000</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X20" s="3">
         <v>-24000</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-35000</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-30000</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>397500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>397500</v>
+      </c>
+      <c r="F21" s="3">
         <v>253000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>253000</v>
       </c>
-      <c r="F21" s="3">
-        <v>267500</v>
-      </c>
-      <c r="G21" s="3">
-        <v>267500</v>
-      </c>
       <c r="H21" s="3">
+        <v>299500</v>
+      </c>
+      <c r="I21" s="3">
+        <v>299500</v>
+      </c>
+      <c r="J21" s="3">
         <v>270500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>270500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>214500</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N21" s="3">
         <v>842000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="3">
         <v>641000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>661000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="3">
         <v>647000</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V21" s="3">
         <v>569000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X21" s="3">
         <v>724000</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z21" s="3">
         <v>630000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>984000</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC21" s="3">
         <v>541000</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>35000</v>
+        <v>37500</v>
       </c>
       <c r="E22" s="3">
-        <v>35000</v>
+        <v>37500</v>
       </c>
       <c r="F22" s="3">
         <v>35000</v>
@@ -1719,38 +1798,38 @@
         <v>35000</v>
       </c>
       <c r="H22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="I22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="J22" s="3">
         <v>31000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>31000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>22500</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q22" s="3">
         <v>27000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>30000</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>5</v>
       </c>
@@ -1766,174 +1845,192 @@
       <c r="W22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z22" s="3">
         <v>28000</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>122500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>122500</v>
+      </c>
+      <c r="F23" s="3">
         <v>126500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>126500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>39500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>39500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>105500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>105500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>15500</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N23" s="3">
         <v>280000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-34000</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q23" s="3">
         <v>360000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>383000</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T23" s="3">
         <v>440000</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V23" s="3">
         <v>341000</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X23" s="3">
         <v>496000</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z23" s="3">
         <v>383000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>735000</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC23" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E24" s="3">
+        <v>23500</v>
+      </c>
+      <c r="F24" s="3">
         <v>19500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>19500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-6000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>-6000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>19500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>19500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-7500</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N24" s="3">
         <v>-68000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-134000</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q24" s="3">
         <v>69000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>74000</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T24" s="3">
         <v>51000</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V24" s="3">
         <v>67000</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X24" s="3">
         <v>21000</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z24" s="3">
         <v>59000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>192000</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC24" s="3">
         <v>86000</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2009,162 +2106,180 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>99000</v>
+      </c>
+      <c r="F26" s="3">
         <v>107000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>107000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>45500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>45500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>86000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>86000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>23000</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N26" s="3">
         <v>348000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>100000</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q26" s="3">
         <v>291000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>309000</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T26" s="3">
         <v>389000</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V26" s="3">
         <v>274000</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X26" s="3">
         <v>475000</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z26" s="3">
         <v>324000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>543000</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC26" s="3">
         <v>241000</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>99000</v>
+      </c>
+      <c r="F27" s="3">
         <v>107000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>107000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>45500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>45500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>86000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>86000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>23000</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N27" s="3">
         <v>348000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>100000</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="3">
         <v>291000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>309000</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T27" s="3">
         <v>389000</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V27" s="3">
         <v>274000</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X27" s="3">
         <v>475000</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z27" s="3">
         <v>324000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>543000</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC27" s="3">
         <v>241000</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2240,8 +2355,14 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2281,33 +2402,33 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>5</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V29" s="3">
+      <c r="V29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X29" s="3">
         <v>-32000</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2317,8 +2438,14 @@
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2394,8 +2521,14 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2471,162 +2604,180 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-7000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-7000</v>
       </c>
-      <c r="F32" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-5000</v>
-      </c>
       <c r="H32" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="I32" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="J32" s="3">
         <v>-10000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-10000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-67000</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
         <v>20000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>29000</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="3">
         <v>9000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>6000</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T32" s="3">
         <v>51000</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V32" s="3">
         <v>31000</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X32" s="3">
         <v>24000</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z32" s="3">
         <v>3000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>35000</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC32" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>99000</v>
+      </c>
+      <c r="F33" s="3">
         <v>107000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>107000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>45500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>45500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>86000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>86000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>23000</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N33" s="3">
         <v>348000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>100000</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="3">
         <v>291000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>309000</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T33" s="3">
         <v>389000</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V33" s="3">
         <v>274000</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X33" s="3">
         <v>443000</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z33" s="3">
         <v>324000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>543000</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC33" s="3">
         <v>241000</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2702,167 +2853,185 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>99000</v>
+      </c>
+      <c r="F35" s="3">
         <v>107000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>107000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>45500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>45500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>86000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>86000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>23000</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N35" s="3">
         <v>348000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>100000</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="3">
         <v>291000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>309000</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T35" s="3">
         <v>389000</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V35" s="3">
         <v>274000</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X35" s="3">
         <v>443000</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z35" s="3">
         <v>324000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>543000</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC35" s="3">
         <v>241000</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45472</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45380</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45108</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45017</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44289</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44196</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44009</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43918</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43830</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43645</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43554</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43465</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43372</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43281</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43190</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43100</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43008</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42917</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42735</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42644</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42553</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2890,8 +3059,10 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2919,85 +3090,93 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>619000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>619000</v>
+      </c>
+      <c r="F41" s="3">
         <v>568000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>568000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>302000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>302000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>190000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>190000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>350000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1762000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>347000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>277000</v>
-      </c>
-      <c r="N41" s="3">
-        <v>137000</v>
-      </c>
-      <c r="O41" s="3">
-        <v>365000</v>
       </c>
       <c r="P41" s="3">
         <v>137000</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>5</v>
+      <c r="Q41" s="3">
+        <v>365000</v>
       </c>
       <c r="R41" s="3">
+        <v>137000</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T41" s="3">
         <v>365000</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V41" s="3">
         <v>99000</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X41" s="3">
         <v>169000</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z41" s="3">
         <v>69000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>100000</v>
       </c>
-      <c r="Z41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC41" s="3">
         <v>85000</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3073,192 +3252,210 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1241000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1241000</v>
+      </c>
+      <c r="F43" s="3">
         <v>1399000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1399000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1214000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1214000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1277000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1277000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1178000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1211000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1231000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1328000</v>
-      </c>
-      <c r="N43" s="3">
-        <v>1280000</v>
-      </c>
-      <c r="O43" s="3">
-        <v>1317000</v>
       </c>
       <c r="P43" s="3">
         <v>1280000</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>5</v>
+      <c r="Q43" s="3">
+        <v>1317000</v>
       </c>
       <c r="R43" s="3">
+        <v>1280000</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T43" s="3">
         <v>1317000</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V43" s="3">
         <v>1205000</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X43" s="3">
         <v>1258000</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z43" s="3">
         <v>1212000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>1185000</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC43" s="3">
         <v>1166000</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2387000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2387000</v>
+      </c>
+      <c r="F44" s="3">
         <v>2491000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>2491000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>2395000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>2395000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>2411000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>2411000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>2205000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>1691000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>1721000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1614000</v>
-      </c>
-      <c r="N44" s="3">
-        <v>1532000</v>
-      </c>
-      <c r="O44" s="3">
-        <v>1395000</v>
       </c>
       <c r="P44" s="3">
         <v>1532000</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>5</v>
+      <c r="Q44" s="3">
+        <v>1395000</v>
       </c>
       <c r="R44" s="3">
+        <v>1532000</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T44" s="3">
         <v>1395000</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V44" s="3">
         <v>1352000</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X44" s="3">
         <v>1304000</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z44" s="3">
         <v>1298000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>1244000</v>
       </c>
-      <c r="Z44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC44" s="3">
         <v>1291000</v>
       </c>
     </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="D45" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>47000</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3">
         <v>27000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>27000</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L45" s="3">
         <v>47000</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -3295,102 +3492,114 @@
       <c r="X45" s="3">
         <v>0</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA45" s="3">
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC45" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4421000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4421000</v>
+      </c>
+      <c r="F46" s="3">
         <v>4458000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>4458000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>4030000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>4030000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3878000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>3878000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>3856000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>4664000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>3299000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>3219000</v>
-      </c>
-      <c r="N46" s="3">
-        <v>2949000</v>
-      </c>
-      <c r="O46" s="3">
-        <v>3077000</v>
       </c>
       <c r="P46" s="3">
         <v>2949000</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>5</v>
+      <c r="Q46" s="3">
+        <v>3077000</v>
       </c>
       <c r="R46" s="3">
+        <v>2949000</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T46" s="3">
         <v>3077000</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V46" s="3">
         <v>2656000</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X46" s="3">
         <v>2731000</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z46" s="3">
         <v>2579000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>2529000</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC46" s="3">
         <v>2552000</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>24000</v>
+        <v>16000</v>
       </c>
       <c r="E47" s="3">
-        <v>24000</v>
+        <v>16000</v>
       </c>
       <c r="F47" s="3">
         <v>24000</v>
@@ -3399,221 +3608,239 @@
         <v>24000</v>
       </c>
       <c r="H47" s="3">
+        <v>24000</v>
+      </c>
+      <c r="I47" s="3">
+        <v>24000</v>
+      </c>
+      <c r="J47" s="3">
         <v>35000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>35000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>58000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>117000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>106000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>110000</v>
-      </c>
-      <c r="N47" s="3">
-        <v>109000</v>
-      </c>
-      <c r="O47" s="3">
-        <v>139000</v>
       </c>
       <c r="P47" s="3">
         <v>109000</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>5</v>
+      <c r="Q47" s="3">
+        <v>139000</v>
       </c>
       <c r="R47" s="3">
+        <v>109000</v>
+      </c>
+      <c r="S47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T47" s="3">
         <v>139000</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V47" s="3">
         <v>140000</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X47" s="3">
         <v>139000</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z47" s="3">
         <v>135000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>137000</v>
       </c>
-      <c r="Z47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC47" s="3">
         <v>127000</v>
       </c>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1422000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1422000</v>
+      </c>
+      <c r="F48" s="3">
         <v>1441000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1441000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1470000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1470000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1421000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1421000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1455000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1449000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1353000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1323000</v>
-      </c>
-      <c r="N48" s="3">
-        <v>1226000</v>
-      </c>
-      <c r="O48" s="3">
-        <v>1062000</v>
       </c>
       <c r="P48" s="3">
         <v>1226000</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>5</v>
+      <c r="Q48" s="3">
+        <v>1062000</v>
       </c>
       <c r="R48" s="3">
+        <v>1226000</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T48" s="3">
         <v>1062000</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V48" s="3">
         <v>1056000</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X48" s="3">
         <v>1049000</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z48" s="3">
         <v>1032000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>982000</v>
       </c>
-      <c r="Z48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC48" s="3">
         <v>946000</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4058000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>4058000</v>
+      </c>
+      <c r="F49" s="3">
         <v>4216000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>4216000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>4102000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>4102000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>4229000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>4229000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>4267000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>4414000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>4398000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>4356000</v>
-      </c>
-      <c r="N49" s="3">
-        <v>4391000</v>
-      </c>
-      <c r="O49" s="3">
-        <v>3547000</v>
       </c>
       <c r="P49" s="3">
         <v>4391000</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>5</v>
+      <c r="Q49" s="3">
+        <v>3547000</v>
       </c>
       <c r="R49" s="3">
+        <v>4391000</v>
+      </c>
+      <c r="S49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T49" s="3">
         <v>3547000</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V49" s="3">
         <v>3638000</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X49" s="3">
         <v>3742000</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z49" s="3">
         <v>3587000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>3599000</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC49" s="3">
         <v>3762000</v>
       </c>
     </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3689,8 +3916,14 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3766,85 +3999,97 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>87000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>87000</v>
+      </c>
+      <c r="F52" s="3">
         <v>84000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>84000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>87000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>87000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>93000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>93000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>153000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>368000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>383000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>291000</v>
-      </c>
-      <c r="N52" s="3">
-        <v>271000</v>
-      </c>
-      <c r="O52" s="3">
-        <v>234000</v>
       </c>
       <c r="P52" s="3">
         <v>271000</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>5</v>
+      <c r="Q52" s="3">
+        <v>234000</v>
       </c>
       <c r="R52" s="3">
+        <v>271000</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T52" s="3">
         <v>234000</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V52" s="3">
         <v>223000</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X52" s="3">
         <v>205000</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z52" s="3">
         <v>106000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>97000</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC52" s="3">
         <v>115000</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3920,85 +4165,97 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10354000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>10354000</v>
+      </c>
+      <c r="F54" s="3">
         <v>10542000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>10542000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>9987000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>9987000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>9844000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>9844000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>9966000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>11012000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>9539000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>9299000</v>
-      </c>
-      <c r="N54" s="3">
-        <v>8946000</v>
-      </c>
-      <c r="O54" s="3">
-        <v>8059000</v>
       </c>
       <c r="P54" s="3">
         <v>8946000</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>5</v>
+      <c r="Q54" s="3">
+        <v>8059000</v>
       </c>
       <c r="R54" s="3">
+        <v>8946000</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T54" s="3">
         <v>8059000</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V54" s="3">
         <v>7713000</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X54" s="3">
         <v>7866000</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z54" s="3">
         <v>7439000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>7344000</v>
       </c>
-      <c r="Z54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC54" s="3">
         <v>7502000</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4026,8 +4283,10 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4055,470 +4314,508 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1082000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1082000</v>
+      </c>
+      <c r="F57" s="3">
         <v>1024000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1024000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1016000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1016000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>955000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>955000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1029000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1022000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>875000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1046000</v>
-      </c>
-      <c r="N57" s="3">
-        <v>906000</v>
-      </c>
-      <c r="O57" s="3">
-        <v>957000</v>
       </c>
       <c r="P57" s="3">
         <v>906000</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>5</v>
+      <c r="Q57" s="3">
+        <v>957000</v>
       </c>
       <c r="R57" s="3">
+        <v>906000</v>
+      </c>
+      <c r="S57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T57" s="3">
         <v>957000</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V57" s="3">
         <v>831000</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X57" s="3">
         <v>957000</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z57" s="3">
         <v>792000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>884000</v>
       </c>
-      <c r="Z57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC57" s="3">
         <v>842000</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>63000</v>
+      </c>
+      <c r="F58" s="3">
         <v>380000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>380000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>765000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>765000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>407000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>407000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>160000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>337000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>163000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>72000</v>
-      </c>
-      <c r="N58" s="3">
-        <v>199000</v>
-      </c>
-      <c r="O58" s="3">
-        <v>164000</v>
       </c>
       <c r="P58" s="3">
         <v>199000</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>5</v>
+      <c r="Q58" s="3">
+        <v>164000</v>
       </c>
       <c r="R58" s="3">
+        <v>199000</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T58" s="3">
         <v>164000</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V58" s="3">
         <v>86000</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X58" s="3">
         <v>27000</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z58" s="3">
         <v>64000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>86000</v>
       </c>
-      <c r="Z58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC58" s="3">
         <v>71000</v>
       </c>
     </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>386000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>386000</v>
+      </c>
+      <c r="F59" s="3">
         <v>373000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>373000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>490000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>490000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>405000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>405000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>526000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>329000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>478000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>446000</v>
-      </c>
-      <c r="N59" s="3">
-        <v>369000</v>
-      </c>
-      <c r="O59" s="3">
-        <v>344000</v>
       </c>
       <c r="P59" s="3">
         <v>369000</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>5</v>
+      <c r="Q59" s="3">
+        <v>344000</v>
       </c>
       <c r="R59" s="3">
+        <v>369000</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T59" s="3">
         <v>344000</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V59" s="3">
         <v>330000</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X59" s="3">
         <v>362000</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z59" s="3">
         <v>329000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>378000</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC59" s="3">
         <v>432000</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1531000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1531000</v>
+      </c>
+      <c r="F60" s="3">
         <v>1777000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1777000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>2271000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>2271000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1767000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1767000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1715000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1688000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1516000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1564000</v>
-      </c>
-      <c r="N60" s="3">
-        <v>1474000</v>
-      </c>
-      <c r="O60" s="3">
-        <v>1465000</v>
       </c>
       <c r="P60" s="3">
         <v>1474000</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>5</v>
+      <c r="Q60" s="3">
+        <v>1465000</v>
       </c>
       <c r="R60" s="3">
+        <v>1474000</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T60" s="3">
         <v>1465000</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V60" s="3">
         <v>1247000</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X60" s="3">
         <v>1346000</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z60" s="3">
         <v>1185000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>1348000</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC60" s="3">
         <v>1345000</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3258000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>3258000</v>
+      </c>
+      <c r="F61" s="3">
         <v>3275000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>3275000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>2319000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>2319000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2633000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2633000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2712000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>3353000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2476000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1975000</v>
-      </c>
-      <c r="N61" s="3">
-        <v>1980000</v>
-      </c>
-      <c r="O61" s="3">
-        <v>1301000</v>
       </c>
       <c r="P61" s="3">
         <v>1980000</v>
       </c>
       <c r="Q61" s="3">
-        <v>0</v>
+        <v>1301000</v>
       </c>
       <c r="R61" s="3">
+        <v>1980000</v>
+      </c>
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>1301000</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>1420000</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>1423000</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>1604000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>1564000</v>
       </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
         <v>1708000</v>
       </c>
     </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>190000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>190000</v>
+      </c>
+      <c r="F62" s="3">
         <v>167000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>167000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>83000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>83000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>137000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>137000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>174000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>692000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>587000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>619000</v>
-      </c>
-      <c r="N62" s="3">
-        <v>540000</v>
-      </c>
-      <c r="O62" s="3">
-        <v>419000</v>
       </c>
       <c r="P62" s="3">
         <v>540000</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>5</v>
+      <c r="Q62" s="3">
+        <v>419000</v>
       </c>
       <c r="R62" s="3">
+        <v>540000</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T62" s="3">
         <v>419000</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V62" s="3">
         <v>403000</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X62" s="3">
         <v>453000</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z62" s="3">
         <v>449000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>474000</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC62" s="3">
         <v>505000</v>
       </c>
     </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4594,8 +4891,14 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4671,8 +4974,14 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4748,85 +5057,97 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5089000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>5089000</v>
+      </c>
+      <c r="F66" s="3">
         <v>5337000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>5337000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>4770000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>4770000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>4611000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>4611000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>4707000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>5733000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>4579000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>4158000</v>
-      </c>
-      <c r="N66" s="3">
-        <v>3994000</v>
-      </c>
-      <c r="O66" s="3">
-        <v>3185000</v>
       </c>
       <c r="P66" s="3">
         <v>3994000</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>5</v>
+      <c r="Q66" s="3">
+        <v>3185000</v>
       </c>
       <c r="R66" s="3">
+        <v>3994000</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T66" s="3">
         <v>3185000</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V66" s="3">
         <v>3070000</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X66" s="3">
         <v>3222000</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z66" s="3">
         <v>3238000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>3386000</v>
       </c>
-      <c r="Z66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC66" s="3">
         <v>3558000</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4854,8 +5175,10 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4931,8 +5254,14 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5008,8 +5337,14 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5085,8 +5420,14 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5162,85 +5503,97 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5018000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>5018000</v>
+      </c>
+      <c r="F72" s="3">
         <v>4934000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>4934000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>4906000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>4906000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>4963000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>4963000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>5026000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>4647000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>4349000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>4543000</v>
-      </c>
-      <c r="N72" s="3">
-        <v>4370000</v>
-      </c>
-      <c r="O72" s="3">
-        <v>4303000</v>
       </c>
       <c r="P72" s="3">
         <v>4370000</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>5</v>
+      <c r="Q72" s="3">
+        <v>4303000</v>
       </c>
       <c r="R72" s="3">
+        <v>4370000</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T72" s="3">
         <v>4303000</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V72" s="3">
         <v>4092000</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X72" s="3">
         <v>4118000</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z72" s="3">
         <v>3680000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>3610000</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC72" s="3">
         <v>3450000</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5316,8 +5669,14 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5393,8 +5752,14 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5470,85 +5835,97 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5265000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5265000</v>
+      </c>
+      <c r="F76" s="3">
         <v>5205000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>5205000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5217000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>5217000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>5233000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>5233000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>5259000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>5279000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>4960000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>5141000</v>
-      </c>
-      <c r="N76" s="3">
-        <v>4952000</v>
-      </c>
-      <c r="O76" s="3">
-        <v>4874000</v>
       </c>
       <c r="P76" s="3">
         <v>4952000</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>5</v>
+      <c r="Q76" s="3">
+        <v>4874000</v>
       </c>
       <c r="R76" s="3">
+        <v>4952000</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T76" s="3">
         <v>4874000</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V76" s="3">
         <v>4643000</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X76" s="3">
         <v>4644000</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z76" s="3">
         <v>4201000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>3958000</v>
       </c>
-      <c r="Z76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC76" s="3">
         <v>3944000</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5624,167 +6001,185 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45472</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45380</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45108</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45017</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44289</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44196</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44009</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43918</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43830</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43645</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43554</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43465</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43372</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43281</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43190</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43100</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43008</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42917</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42735</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42644</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42553</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>99000</v>
+      </c>
+      <c r="F81" s="3">
         <v>107000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>107000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>45500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>45500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>86000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>86000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>23000</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N81" s="3">
         <v>348000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>100000</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q81" s="3">
         <v>291000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>309000</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T81" s="3">
         <v>389000</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V81" s="3">
         <v>274000</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X81" s="3">
         <v>443000</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z81" s="3">
         <v>324000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>543000</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC81" s="3">
         <v>241000</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5812,61 +6207,63 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>61000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>61000</v>
+      </c>
+      <c r="F83" s="3">
         <v>92000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>92000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>57500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>57500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>102000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>102000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>59000</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="3">
         <v>562000</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q83" s="3">
         <v>254000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>248000</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3">
         <v>207000</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T83" s="3">
-        <v>228000</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>5</v>
@@ -5878,19 +6275,25 @@
         <v>5</v>
       </c>
       <c r="X83" s="3">
+        <v>228000</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z83" s="3">
         <v>219000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>249000</v>
       </c>
-      <c r="Z83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC83" s="3">
         <v>214000</v>
       </c>
     </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5966,8 +6369,14 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6043,8 +6452,14 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6120,8 +6535,14 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6197,8 +6618,14 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6274,85 +6701,97 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>374500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>374500</v>
+      </c>
+      <c r="F89" s="3">
         <v>119000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>119000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>247500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>247500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>56500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>56500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>130500</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N89" s="3">
         <v>935000</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q89" s="3">
         <v>717000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>451000</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3">
         <v>634000</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V89" s="3">
         <v>297000</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X89" s="3">
         <v>739000</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z89" s="3">
         <v>351000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>580000</v>
       </c>
-      <c r="Z89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC89" s="3">
         <v>269000</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6380,85 +6819,93 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-104500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-104500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-86000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-86000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-130000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-130000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-83500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-83500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-92500</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-255000</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-188000</v>
       </c>
       <c r="M91" s="3">
         <v>-255000</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>5</v>
+      <c r="N91" s="3">
+        <v>-188000</v>
       </c>
       <c r="O91" s="3">
         <v>-255000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="P91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>-255000</v>
+      </c>
+      <c r="R91" s="3">
         <v>-153000</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T91" s="3">
         <v>-169000</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V91" s="3">
         <v>-178000</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X91" s="3">
         <v>-198000</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-178000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-218000</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-174000</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6534,8 +6981,14 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6611,85 +7064,97 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-104500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-104500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-180000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-180000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-133000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-133000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-91000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-91000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-102000</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N94" s="3">
         <v>-606000</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-286000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-965000</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3">
         <v>-179000</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V94" s="3">
         <v>-199000</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X94" s="3">
         <v>-326000</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-217000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>5000</v>
       </c>
-      <c r="Z94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-388000</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6717,85 +7182,93 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>62500</v>
+      </c>
+      <c r="E96" s="3">
+        <v>62500</v>
+      </c>
+      <c r="F96" s="3">
         <v>101000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>101000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>63000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>63000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>100500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>100500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>62500</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-328000</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-126000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-192000</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-123000</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-198000</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-107000</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-162000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-109000</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-170000</v>
       </c>
     </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6871,8 +7344,14 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6948,8 +7427,14 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7025,144 +7510,156 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-229000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-229000</v>
+      </c>
+      <c r="F100" s="3">
         <v>186000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>186000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-57000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-57000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-43000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-43000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-111000</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N100" s="3">
         <v>1164000</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-296000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>303000</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3">
         <v>-202000</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V100" s="3">
         <v>-169000</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X100" s="3">
         <v>-304000</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-130000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-598000</v>
       </c>
-      <c r="Z100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC100" s="3">
         <v>69000</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-3000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-3000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-1500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-1500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-4000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-4000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-2500</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3">
         <v>1000</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
       </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3">
         <v>-1000</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V101" s="3">
         <v>-3000</v>
-      </c>
-      <c r="U101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V101" s="3">
-        <v>2000</v>
       </c>
       <c r="W101" s="3" t="s">
         <v>5</v>
@@ -7170,90 +7667,102 @@
       <c r="X101" s="3">
         <v>2000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Y101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>36000</v>
+      </c>
+      <c r="F102" s="3">
         <v>122500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>122500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>58500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>58500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-80500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-80500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-84000</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N102" s="3">
         <v>1494000</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q102" s="3">
         <v>135000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-211000</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3">
         <v>252000</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V102" s="3">
         <v>-74000</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X102" s="3">
         <v>111000</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z102" s="3">
         <v>6000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-15000</v>
       </c>
-      <c r="Z102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC102" s="3">
         <v>-49000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SNN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
   <si>
     <t>SNN</t>
   </si>
@@ -656,378 +656,404 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45744</v>
+      </c>
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45472</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45380</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45108</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45017</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44289</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44009</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43918</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43645</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43554</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43465</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43372</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43190</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43100</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43008</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42917</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42735</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42644</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42553</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1480500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1480500</v>
+      </c>
+      <c r="F8" s="3">
         <v>1491500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1491500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1413500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1413500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1407500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1407500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1367000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1367000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1307500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1264000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>2525000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>2035000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1134000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>2653000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>2485000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1202000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>2464000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1169000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>2440000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1196000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>2429000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1152000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>2336000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>2341000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>1119000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>2328000</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>435000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>435000</v>
+      </c>
+      <c r="F9" s="3">
         <v>439000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>439000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>426500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>426500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>409000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>409000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>418000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>418000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>373500</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="3">
         <v>750000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>646000</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S9" s="3">
         <v>690000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>648000</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V9" s="3">
         <v>645000</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X9" s="3">
         <v>653000</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z9" s="3">
         <v>645000</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB9" s="3">
         <v>603000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>640000</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE9" s="3">
         <v>632000</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1045500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1045500</v>
+      </c>
+      <c r="F10" s="3">
         <v>1052500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1052500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>987000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>987000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>998500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>998500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>949000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>949000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>934000</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="3">
         <v>1775000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1389000</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="3">
         <v>1963000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1837000</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V10" s="3">
         <v>1819000</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X10" s="3">
         <v>1787000</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z10" s="3">
         <v>1784000</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB10" s="3">
         <v>1733000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>1701000</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE10" s="3">
         <v>1696000</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,67 +1083,69 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>71500</v>
+      </c>
+      <c r="E12" s="3">
+        <v>71500</v>
+      </c>
+      <c r="F12" s="3">
         <v>76000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>76000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>68500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>68500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>77000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>77000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>83000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>83000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>80500</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P12" s="3">
         <v>159000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>148000</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S12" s="3">
         <v>153000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>139000</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V12" s="3">
         <v>130000</v>
-      </c>
-      <c r="U12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V12" s="3">
-        <v>116000</v>
       </c>
       <c r="W12" s="3" t="s">
         <v>5</v>
@@ -1129,19 +1157,25 @@
         <v>5</v>
       </c>
       <c r="Z12" s="3">
+        <v>116000</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB12" s="3">
         <v>107000</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AC12" s="3">
         <v>117000</v>
       </c>
-      <c r="AB12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE12" s="3">
         <v>113000</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,174 +1257,192 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>116500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>116500</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>158500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>158500</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>112000</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3">
         <v>74000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>94000</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="3">
         <v>123000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>52000</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="3">
         <v>56000</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" s="3">
         <v>78000</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-30000</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB14" s="3">
         <v>14000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>-326000</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>136500</v>
+      </c>
+      <c r="E15" s="3">
+        <v>136500</v>
+      </c>
+      <c r="F15" s="3">
         <v>128500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>128500</v>
       </c>
-      <c r="F15" s="3">
-        <v>96000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>96000</v>
-      </c>
       <c r="H15" s="3">
+        <v>136500</v>
+      </c>
+      <c r="I15" s="3">
+        <v>136500</v>
+      </c>
+      <c r="J15" s="3">
         <v>74500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>74500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>143000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>143000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>70000</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P15" s="3">
         <v>151000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>83000</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S15" s="3">
         <v>100000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>61000</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V15" s="3">
         <v>56000</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X15" s="3">
         <v>57000</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z15" s="3">
         <v>127000</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB15" s="3">
         <v>65000</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1469,188 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1266000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1266000</v>
+      </c>
+      <c r="F17" s="3">
         <v>1212500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1212500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1249500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1249500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1174500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1174500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1229500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1229500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1096000</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P17" s="3">
         <v>2225000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>2040000</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S17" s="3">
         <v>2257000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>2066000</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V17" s="3">
         <v>1973000</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X17" s="3">
         <v>2068000</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z17" s="3">
         <v>1909000</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB17" s="3">
         <v>1922000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>1571000</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE17" s="3">
         <v>1971000</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>214500</v>
+      </c>
+      <c r="E18" s="3">
+        <v>214500</v>
+      </c>
+      <c r="F18" s="3">
         <v>279000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>279000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>164000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>164000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>233000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>233000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>137500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>137500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>211500</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P18" s="3">
         <v>300000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-5000</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S18" s="3">
         <v>396000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>419000</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V18" s="3">
         <v>491000</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X18" s="3">
         <v>372000</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z18" s="3">
         <v>520000</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB18" s="3">
         <v>414000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>770000</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE18" s="3">
         <v>357000</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,188 +1680,202 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E20" s="3">
+        <v>6500</v>
+      </c>
+      <c r="F20" s="3">
         <v>10000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>10000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>7000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>7000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>8000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>8000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>10000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>10000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>67000</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="3">
         <v>-20000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-29000</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S20" s="3">
         <v>-9000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-6000</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V20" s="3">
         <v>-51000</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X20" s="3">
         <v>-31000</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-24000</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-35000</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-30000</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>344500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>344500</v>
+      </c>
+      <c r="F21" s="3">
         <v>397500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>397500</v>
       </c>
-      <c r="F21" s="3">
-        <v>253000</v>
-      </c>
-      <c r="G21" s="3">
-        <v>253000</v>
-      </c>
       <c r="H21" s="3">
+        <v>293500</v>
+      </c>
+      <c r="I21" s="3">
+        <v>293500</v>
+      </c>
+      <c r="J21" s="3">
         <v>299500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>299500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>270500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>270500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>214500</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3">
         <v>842000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S21" s="3">
         <v>641000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>661000</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V21" s="3">
         <v>647000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X21" s="3">
         <v>569000</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z21" s="3">
         <v>724000</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB21" s="3">
         <v>630000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>984000</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE21" s="3">
         <v>541000</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E22" s="3">
+        <v>34500</v>
+      </c>
+      <c r="F22" s="3">
         <v>37500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>37500</v>
-      </c>
-      <c r="F22" s="3">
-        <v>35000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>35000</v>
       </c>
       <c r="H22" s="3">
         <v>35000</v>
@@ -1804,38 +1884,38 @@
         <v>35000</v>
       </c>
       <c r="J22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="K22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="L22" s="3">
         <v>31000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>31000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>22500</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S22" s="3">
         <v>27000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>30000</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U22" s="3" t="s">
         <v>5</v>
       </c>
@@ -1851,186 +1931,204 @@
       <c r="Y22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="Z22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB22" s="3">
         <v>28000</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>181000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>181000</v>
+      </c>
+      <c r="F23" s="3">
         <v>122500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>122500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>126500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>126500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>39500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>39500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>105500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>105500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>15500</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P23" s="3">
         <v>280000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-34000</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S23" s="3">
         <v>360000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>383000</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V23" s="3">
         <v>440000</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X23" s="3">
         <v>341000</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z23" s="3">
         <v>496000</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB23" s="3">
         <v>383000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>735000</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE23" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E24" s="3">
+        <v>34500</v>
+      </c>
+      <c r="F24" s="3">
         <v>23500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>23500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>19500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>19500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>-6000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-6000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>19500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>19500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>-7500</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P24" s="3">
         <v>-68000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-134000</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S24" s="3">
         <v>69000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>74000</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V24" s="3">
         <v>51000</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X24" s="3">
         <v>67000</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z24" s="3">
         <v>21000</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB24" s="3">
         <v>59000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>192000</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE24" s="3">
         <v>86000</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2210,192 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>146500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>146500</v>
+      </c>
+      <c r="F26" s="3">
         <v>99000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>99000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>107000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>107000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>45500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>45500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>86000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>86000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>23000</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P26" s="3">
         <v>348000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>100000</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S26" s="3">
         <v>291000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>309000</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V26" s="3">
         <v>389000</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X26" s="3">
         <v>274000</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z26" s="3">
         <v>475000</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB26" s="3">
         <v>324000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>543000</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE26" s="3">
         <v>241000</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>146500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>146500</v>
+      </c>
+      <c r="F27" s="3">
         <v>99000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>99000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>107000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>107000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>45500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>45500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>86000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>86000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>23000</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P27" s="3">
         <v>348000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>100000</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S27" s="3">
         <v>291000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>309000</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V27" s="3">
         <v>389000</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X27" s="3">
         <v>274000</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z27" s="3">
         <v>475000</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB27" s="3">
         <v>324000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>543000</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE27" s="3">
         <v>241000</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2477,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2408,33 +2530,33 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-32000</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2444,8 +2566,14 @@
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2655,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,174 +2744,192 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="F32" s="3">
         <v>-10000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-10000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-7000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-7000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-8000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-8000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-10000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-10000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-67000</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P32" s="3">
         <v>20000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>29000</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S32" s="3">
         <v>9000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>6000</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V32" s="3">
         <v>51000</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X32" s="3">
         <v>31000</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z32" s="3">
         <v>24000</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB32" s="3">
         <v>3000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>35000</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE32" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>146500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>146500</v>
+      </c>
+      <c r="F33" s="3">
         <v>99000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>99000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>107000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>107000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>45500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>45500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>86000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>86000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>23000</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P33" s="3">
         <v>348000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>100000</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S33" s="3">
         <v>291000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>309000</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V33" s="3">
         <v>389000</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X33" s="3">
         <v>274000</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z33" s="3">
         <v>443000</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB33" s="3">
         <v>324000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>543000</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE33" s="3">
         <v>241000</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +3011,197 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>146500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>146500</v>
+      </c>
+      <c r="F35" s="3">
         <v>99000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>99000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>107000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>107000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>45500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>45500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>86000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>86000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>23000</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P35" s="3">
         <v>348000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>100000</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S35" s="3">
         <v>291000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>309000</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V35" s="3">
         <v>389000</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X35" s="3">
         <v>274000</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z35" s="3">
         <v>443000</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB35" s="3">
         <v>324000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>543000</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE35" s="3">
         <v>241000</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45744</v>
+      </c>
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45472</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45380</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45108</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45017</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44289</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44009</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43918</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43645</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43554</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43465</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43372</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43190</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43100</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43008</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42917</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42735</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42644</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42553</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3231,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,91 +3264,99 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>676000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>676000</v>
+      </c>
+      <c r="F41" s="3">
         <v>619000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>619000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>568000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>568000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>302000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>302000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>190000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>190000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>350000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1762000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>347000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>277000</v>
-      </c>
-      <c r="P41" s="3">
-        <v>137000</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>365000</v>
       </c>
       <c r="R41" s="3">
         <v>137000</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>5</v>
+      <c r="S41" s="3">
+        <v>365000</v>
       </c>
       <c r="T41" s="3">
+        <v>137000</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V41" s="3">
         <v>365000</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X41" s="3">
         <v>99000</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z41" s="3">
         <v>169000</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB41" s="3">
         <v>69000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>100000</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE41" s="3">
         <v>85000</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3258,210 +3438,228 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1484000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1484000</v>
+      </c>
+      <c r="F43" s="3">
         <v>1241000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1241000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1399000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1399000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1214000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1214000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1277000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1277000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1178000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1211000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1231000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1328000</v>
-      </c>
-      <c r="P43" s="3">
-        <v>1280000</v>
-      </c>
-      <c r="Q43" s="3">
-        <v>1317000</v>
       </c>
       <c r="R43" s="3">
         <v>1280000</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>5</v>
+      <c r="S43" s="3">
+        <v>1317000</v>
       </c>
       <c r="T43" s="3">
+        <v>1280000</v>
+      </c>
+      <c r="U43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V43" s="3">
         <v>1317000</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X43" s="3">
         <v>1205000</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z43" s="3">
         <v>1258000</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB43" s="3">
         <v>1212000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>1185000</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE43" s="3">
         <v>1166000</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2467000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2467000</v>
+      </c>
+      <c r="F44" s="3">
         <v>2387000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>2387000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>2491000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>2491000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>2395000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>2395000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>2411000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>2411000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>2205000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>1691000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>1721000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1614000</v>
-      </c>
-      <c r="P44" s="3">
-        <v>1532000</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>1395000</v>
       </c>
       <c r="R44" s="3">
         <v>1532000</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>5</v>
+      <c r="S44" s="3">
+        <v>1395000</v>
       </c>
       <c r="T44" s="3">
+        <v>1532000</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V44" s="3">
         <v>1395000</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X44" s="3">
         <v>1352000</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z44" s="3">
         <v>1304000</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB44" s="3">
         <v>1298000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>1244000</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE44" s="3">
         <v>1291000</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3">
         <v>47000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>47000</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3">
         <v>27000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>27000</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N45" s="3">
         <v>47000</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
       <c r="O45" s="3">
         <v>0</v>
       </c>
@@ -3498,114 +3696,126 @@
       <c r="Z45" s="3">
         <v>0</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC45" s="3">
+      <c r="AA45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE45" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4627000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4627000</v>
+      </c>
+      <c r="F46" s="3">
         <v>4421000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>4421000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>4458000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>4458000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>4030000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>4030000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>3878000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>3878000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>3856000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>4664000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>3299000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>3219000</v>
-      </c>
-      <c r="P46" s="3">
-        <v>2949000</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>3077000</v>
       </c>
       <c r="R46" s="3">
         <v>2949000</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>5</v>
+      <c r="S46" s="3">
+        <v>3077000</v>
       </c>
       <c r="T46" s="3">
+        <v>2949000</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V46" s="3">
         <v>3077000</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X46" s="3">
         <v>2656000</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z46" s="3">
         <v>2731000</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB46" s="3">
         <v>2579000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>2529000</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE46" s="3">
         <v>2552000</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>36000</v>
+      </c>
+      <c r="F47" s="3">
         <v>16000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>16000</v>
-      </c>
-      <c r="F47" s="3">
-        <v>24000</v>
-      </c>
-      <c r="G47" s="3">
-        <v>24000</v>
       </c>
       <c r="H47" s="3">
         <v>24000</v>
@@ -3614,233 +3824,251 @@
         <v>24000</v>
       </c>
       <c r="J47" s="3">
+        <v>24000</v>
+      </c>
+      <c r="K47" s="3">
+        <v>24000</v>
+      </c>
+      <c r="L47" s="3">
         <v>35000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>35000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>58000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>117000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>106000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>110000</v>
-      </c>
-      <c r="P47" s="3">
-        <v>109000</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>139000</v>
       </c>
       <c r="R47" s="3">
         <v>109000</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>5</v>
+      <c r="S47" s="3">
+        <v>139000</v>
       </c>
       <c r="T47" s="3">
+        <v>109000</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V47" s="3">
         <v>139000</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X47" s="3">
         <v>140000</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z47" s="3">
         <v>139000</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB47" s="3">
         <v>135000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>137000</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE47" s="3">
         <v>127000</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1436000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1436000</v>
+      </c>
+      <c r="F48" s="3">
         <v>1422000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1422000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1441000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1441000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1470000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1470000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1421000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1421000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1455000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1449000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1353000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1323000</v>
-      </c>
-      <c r="P48" s="3">
-        <v>1226000</v>
-      </c>
-      <c r="Q48" s="3">
-        <v>1062000</v>
       </c>
       <c r="R48" s="3">
         <v>1226000</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>5</v>
+      <c r="S48" s="3">
+        <v>1062000</v>
       </c>
       <c r="T48" s="3">
+        <v>1226000</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V48" s="3">
         <v>1062000</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X48" s="3">
         <v>1056000</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z48" s="3">
         <v>1049000</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB48" s="3">
         <v>1032000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>982000</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE48" s="3">
         <v>946000</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4073000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>4073000</v>
+      </c>
+      <c r="F49" s="3">
         <v>4058000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>4058000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>4216000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>4216000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>4102000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>4102000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>4229000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>4229000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>4267000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>4414000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>4398000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>4356000</v>
-      </c>
-      <c r="P49" s="3">
-        <v>4391000</v>
-      </c>
-      <c r="Q49" s="3">
-        <v>3547000</v>
       </c>
       <c r="R49" s="3">
         <v>4391000</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>5</v>
+      <c r="S49" s="3">
+        <v>3547000</v>
       </c>
       <c r="T49" s="3">
+        <v>4391000</v>
+      </c>
+      <c r="U49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V49" s="3">
         <v>3547000</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X49" s="3">
         <v>3638000</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z49" s="3">
         <v>3742000</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB49" s="3">
         <v>3587000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>3599000</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE49" s="3">
         <v>3762000</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4150,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,91 +4239,103 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>119000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>119000</v>
+      </c>
+      <c r="F52" s="3">
         <v>87000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>87000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>84000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>84000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>87000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>87000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>93000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>93000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>153000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>368000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>383000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>291000</v>
-      </c>
-      <c r="P52" s="3">
-        <v>271000</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>234000</v>
       </c>
       <c r="R52" s="3">
         <v>271000</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>5</v>
+      <c r="S52" s="3">
+        <v>234000</v>
       </c>
       <c r="T52" s="3">
+        <v>271000</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V52" s="3">
         <v>234000</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X52" s="3">
         <v>223000</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z52" s="3">
         <v>205000</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB52" s="3">
         <v>106000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>97000</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE52" s="3">
         <v>115000</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,91 +4417,103 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10692000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>10692000</v>
+      </c>
+      <c r="F54" s="3">
         <v>10354000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>10354000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>10542000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>10542000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>9987000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>9987000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>9844000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>9844000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>9966000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>11012000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>9539000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>9299000</v>
-      </c>
-      <c r="P54" s="3">
-        <v>8946000</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>8059000</v>
       </c>
       <c r="R54" s="3">
         <v>8946000</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>5</v>
+      <c r="S54" s="3">
+        <v>8059000</v>
       </c>
       <c r="T54" s="3">
+        <v>8946000</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V54" s="3">
         <v>8059000</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X54" s="3">
         <v>7713000</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z54" s="3">
         <v>7866000</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB54" s="3">
         <v>7439000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>7344000</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE54" s="3">
         <v>7502000</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4543,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,423 +4576,455 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1097000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1097000</v>
+      </c>
+      <c r="F57" s="3">
         <v>1082000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1082000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1024000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1024000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1016000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1016000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>955000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>955000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>1029000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>1022000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>875000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1046000</v>
-      </c>
-      <c r="P57" s="3">
-        <v>906000</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>957000</v>
       </c>
       <c r="R57" s="3">
         <v>906000</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>5</v>
+      <c r="S57" s="3">
+        <v>957000</v>
       </c>
       <c r="T57" s="3">
+        <v>906000</v>
+      </c>
+      <c r="U57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V57" s="3">
         <v>957000</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X57" s="3">
         <v>831000</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z57" s="3">
         <v>957000</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB57" s="3">
         <v>792000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>884000</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE57" s="3">
         <v>842000</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>157000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>157000</v>
+      </c>
+      <c r="F58" s="3">
         <v>63000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>63000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>380000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>380000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>765000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>765000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>407000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>407000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>160000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>337000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>163000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>72000</v>
-      </c>
-      <c r="P58" s="3">
-        <v>199000</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>164000</v>
       </c>
       <c r="R58" s="3">
         <v>199000</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>5</v>
+      <c r="S58" s="3">
+        <v>164000</v>
       </c>
       <c r="T58" s="3">
+        <v>199000</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V58" s="3">
         <v>164000</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X58" s="3">
         <v>86000</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z58" s="3">
         <v>27000</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB58" s="3">
         <v>64000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>86000</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE58" s="3">
         <v>71000</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>287000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>287000</v>
+      </c>
+      <c r="F59" s="3">
         <v>386000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>386000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>373000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>373000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>490000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>490000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>405000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>405000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>526000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>329000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>478000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>446000</v>
-      </c>
-      <c r="P59" s="3">
-        <v>369000</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>344000</v>
       </c>
       <c r="R59" s="3">
         <v>369000</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>5</v>
+      <c r="S59" s="3">
+        <v>344000</v>
       </c>
       <c r="T59" s="3">
+        <v>369000</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V59" s="3">
         <v>344000</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X59" s="3">
         <v>330000</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z59" s="3">
         <v>362000</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB59" s="3">
         <v>329000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>378000</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE59" s="3">
         <v>432000</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1541000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1541000</v>
+      </c>
+      <c r="F60" s="3">
         <v>1531000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1531000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1777000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1777000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>2271000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2271000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1767000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1767000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1715000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1688000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1516000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1564000</v>
-      </c>
-      <c r="P60" s="3">
-        <v>1474000</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>1465000</v>
       </c>
       <c r="R60" s="3">
         <v>1474000</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>5</v>
+      <c r="S60" s="3">
+        <v>1465000</v>
       </c>
       <c r="T60" s="3">
+        <v>1474000</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V60" s="3">
         <v>1465000</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X60" s="3">
         <v>1247000</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z60" s="3">
         <v>1346000</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB60" s="3">
         <v>1185000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>1348000</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE60" s="3">
         <v>1345000</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3297000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>3297000</v>
+      </c>
+      <c r="F61" s="3">
         <v>3258000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>3258000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>3275000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>3275000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2319000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2319000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2633000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>2633000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2712000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>3353000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>2476000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>1975000</v>
-      </c>
-      <c r="P61" s="3">
-        <v>1980000</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>1301000</v>
       </c>
       <c r="R61" s="3">
         <v>1980000</v>
       </c>
       <c r="S61" s="3">
-        <v>0</v>
+        <v>1301000</v>
       </c>
       <c r="T61" s="3">
+        <v>1980000</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>1301000</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>1420000</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>1423000</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>1604000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>1564000</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
         <v>1708000</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4743,79 +5035,85 @@
         <v>190000</v>
       </c>
       <c r="F62" s="3">
+        <v>190000</v>
+      </c>
+      <c r="G62" s="3">
+        <v>190000</v>
+      </c>
+      <c r="H62" s="3">
         <v>167000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>167000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>83000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>83000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>137000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>137000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>174000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>692000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>587000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>619000</v>
-      </c>
-      <c r="P62" s="3">
-        <v>540000</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>419000</v>
       </c>
       <c r="R62" s="3">
         <v>540000</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>5</v>
+      <c r="S62" s="3">
+        <v>419000</v>
       </c>
       <c r="T62" s="3">
+        <v>540000</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V62" s="3">
         <v>419000</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X62" s="3">
         <v>403000</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z62" s="3">
         <v>453000</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB62" s="3">
         <v>449000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>474000</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE62" s="3">
         <v>505000</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5195,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5284,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,91 +5373,103 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5156000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>5156000</v>
+      </c>
+      <c r="F66" s="3">
         <v>5089000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>5089000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>5337000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>5337000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>4770000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>4770000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>4611000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>4611000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>4707000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>5733000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>4579000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>4158000</v>
-      </c>
-      <c r="P66" s="3">
-        <v>3994000</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>3185000</v>
       </c>
       <c r="R66" s="3">
         <v>3994000</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>5</v>
+      <c r="S66" s="3">
+        <v>3185000</v>
       </c>
       <c r="T66" s="3">
+        <v>3994000</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V66" s="3">
         <v>3185000</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X66" s="3">
         <v>3070000</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z66" s="3">
         <v>3222000</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB66" s="3">
         <v>3238000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>3386000</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE66" s="3">
         <v>3558000</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5499,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5584,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5673,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5426,8 +5762,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,91 +5851,103 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5121000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>5121000</v>
+      </c>
+      <c r="F72" s="3">
         <v>5018000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>5018000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>4934000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>4934000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>4906000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>4906000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>4963000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>4963000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>5026000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>4647000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>4349000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>4543000</v>
-      </c>
-      <c r="P72" s="3">
-        <v>4370000</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>4303000</v>
       </c>
       <c r="R72" s="3">
         <v>4370000</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>5</v>
+      <c r="S72" s="3">
+        <v>4303000</v>
       </c>
       <c r="T72" s="3">
+        <v>4370000</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V72" s="3">
         <v>4303000</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X72" s="3">
         <v>4092000</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z72" s="3">
         <v>4118000</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB72" s="3">
         <v>3680000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>3610000</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE72" s="3">
         <v>3450000</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +6029,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +6118,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,91 +6207,103 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5536000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5536000</v>
+      </c>
+      <c r="F76" s="3">
         <v>5265000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>5265000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5205000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>5205000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>5217000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>5217000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>5233000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>5233000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>5259000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>5279000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>4960000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>5141000</v>
-      </c>
-      <c r="P76" s="3">
-        <v>4952000</v>
-      </c>
-      <c r="Q76" s="3">
-        <v>4874000</v>
       </c>
       <c r="R76" s="3">
         <v>4952000</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>5</v>
+      <c r="S76" s="3">
+        <v>4874000</v>
       </c>
       <c r="T76" s="3">
+        <v>4952000</v>
+      </c>
+      <c r="U76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V76" s="3">
         <v>4874000</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X76" s="3">
         <v>4643000</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z76" s="3">
         <v>4644000</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB76" s="3">
         <v>4201000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>3958000</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE76" s="3">
         <v>3944000</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6385,197 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45744</v>
+      </c>
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45472</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45380</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45108</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45017</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44289</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44009</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43918</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43645</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43554</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43465</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43372</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43190</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43100</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43008</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42917</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42735</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42644</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42553</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>146500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>146500</v>
+      </c>
+      <c r="F81" s="3">
         <v>99000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>99000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>107000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>107000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>45500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>45500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>86000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>86000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>23000</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P81" s="3">
         <v>348000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>100000</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S81" s="3">
         <v>291000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>309000</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V81" s="3">
         <v>389000</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X81" s="3">
         <v>274000</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z81" s="3">
         <v>443000</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB81" s="3">
         <v>324000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>543000</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE81" s="3">
         <v>241000</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,67 +6605,69 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>93000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>93000</v>
+      </c>
+      <c r="F83" s="3">
         <v>61000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>61000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>92000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>92000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>57500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>57500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>102000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>102000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>59000</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P83" s="3">
         <v>562000</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S83" s="3">
         <v>254000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>248000</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V83" s="3">
         <v>207000</v>
-      </c>
-      <c r="U83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V83" s="3">
-        <v>228000</v>
       </c>
       <c r="W83" s="3" t="s">
         <v>5</v>
@@ -6281,19 +6679,25 @@
         <v>5</v>
       </c>
       <c r="Z83" s="3">
+        <v>228000</v>
+      </c>
+      <c r="AA83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB83" s="3">
         <v>219000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>249000</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE83" s="3">
         <v>214000</v>
       </c>
     </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6779,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6868,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6957,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +7046,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,91 +7135,103 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>198000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>198000</v>
+      </c>
+      <c r="F89" s="3">
         <v>374500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>374500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>119000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>119000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>247500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>247500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>56500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>56500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>130500</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P89" s="3">
         <v>935000</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S89" s="3">
         <v>717000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>451000</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V89" s="3">
         <v>634000</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X89" s="3">
         <v>297000</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z89" s="3">
         <v>739000</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB89" s="3">
         <v>351000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>580000</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE89" s="3">
         <v>269000</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,91 +7261,99 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-69500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-69500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-104500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-104500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-86000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-86000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-130000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-130000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-83500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-83500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-92500</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-255000</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-188000</v>
       </c>
       <c r="O91" s="3">
         <v>-255000</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>5</v>
+      <c r="P91" s="3">
+        <v>-188000</v>
       </c>
       <c r="Q91" s="3">
         <v>-255000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="R91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S91" s="3">
+        <v>-255000</v>
+      </c>
+      <c r="T91" s="3">
         <v>-153000</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V91" s="3">
         <v>-169000</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X91" s="3">
         <v>-178000</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-198000</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-178000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-218000</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-174000</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7435,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,91 +7524,103 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-67500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-67500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-104500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-104500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-180000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-180000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-133000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-133000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-91000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-91000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-102000</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P94" s="3">
         <v>-606000</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S94" s="3">
         <v>-286000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-965000</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V94" s="3">
         <v>-179000</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X94" s="3">
         <v>-199000</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-326000</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-217000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>5000</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-388000</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,91 +7650,99 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>101000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>101000</v>
+      </c>
+      <c r="F96" s="3">
         <v>62500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>62500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>101000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>101000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>63000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>63000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>100500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>100500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>62500</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-328000</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-126000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-192000</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-123000</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-198000</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-107000</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-162000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-109000</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-170000</v>
       </c>
     </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7824,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7913,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,156 +8002,168 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-108500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-108500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-229000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-229000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>186000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>186000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-57000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-57000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-43000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-43000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-111000</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P100" s="3">
         <v>1164000</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S100" s="3">
         <v>-296000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>303000</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V100" s="3">
         <v>-202000</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X100" s="3">
         <v>-169000</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-304000</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-130000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-598000</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE100" s="3">
         <v>69000</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="F101" s="3">
         <v>1000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>1000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-3000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-3000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-1500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-1500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-4000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-4000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-2500</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3">
         <v>1000</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>5</v>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
       </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V101" s="3">
         <v>-1000</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X101" s="3">
         <v>-3000</v>
-      </c>
-      <c r="W101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X101" s="3">
-        <v>2000</v>
       </c>
       <c r="Y101" s="3" t="s">
         <v>5</v>
@@ -7673,96 +8171,108 @@
       <c r="Z101" s="3">
         <v>2000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AA101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>28000</v>
+      </c>
+      <c r="F102" s="3">
         <v>36000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>36000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>122500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>122500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>58500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>58500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-80500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-80500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-84000</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P102" s="3">
         <v>1494000</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S102" s="3">
         <v>135000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-211000</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V102" s="3">
         <v>252000</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X102" s="3">
         <v>-74000</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z102" s="3">
         <v>111000</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB102" s="3">
         <v>6000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-15000</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE102" s="3">
         <v>-49000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SNN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SNN_QTR_FIN.xlsx
@@ -656,404 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45836</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45744</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45472</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45380</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45108</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45017</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44289</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44009</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43918</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43645</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43554</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43372</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42917</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42735</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42644</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42553</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1601500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1601500</v>
+      </c>
+      <c r="F8" s="3">
         <v>1480500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1480500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1491500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1491500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1413500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1413500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1407500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1407500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1367000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1367000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1307500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1264000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>2525000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>2035000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1134000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>2653000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>2485000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1202000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>2464000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1169000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>2440000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1196000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>2429000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>1152000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>2336000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>2341000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>1119000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>2328000</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>543500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>543500</v>
+      </c>
+      <c r="F9" s="3">
         <v>435000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>435000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>439000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>439000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>426500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>426500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>409000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>409000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>418000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>418000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>373500</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3">
         <v>750000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>646000</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U9" s="3">
         <v>690000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>648000</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X9" s="3">
         <v>645000</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z9" s="3">
         <v>653000</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB9" s="3">
         <v>645000</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD9" s="3">
         <v>603000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>640000</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG9" s="3">
         <v>632000</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1058000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1058000</v>
+      </c>
+      <c r="F10" s="3">
         <v>1045500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1045500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>1052500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>1052500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>987000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>987000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>998500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>998500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>949000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>949000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>934000</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3">
         <v>1775000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1389000</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U10" s="3">
         <v>1963000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>1837000</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X10" s="3">
         <v>1819000</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z10" s="3">
         <v>1787000</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB10" s="3">
         <v>1784000</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD10" s="3">
         <v>1733000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>1701000</v>
       </c>
-      <c r="AD10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG10" s="3">
         <v>1696000</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1085,73 +1110,75 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>75500</v>
+      </c>
+      <c r="E12" s="3">
+        <v>75500</v>
+      </c>
+      <c r="F12" s="3">
         <v>71500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>71500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>76000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>76000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>68500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>68500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>77000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>77000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>83000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>83000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>80500</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R12" s="3">
         <v>159000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>148000</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U12" s="3">
         <v>153000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="V12" s="3">
         <v>139000</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X12" s="3">
         <v>130000</v>
-      </c>
-      <c r="W12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X12" s="3">
-        <v>116000</v>
       </c>
       <c r="Y12" s="3" t="s">
         <v>5</v>
@@ -1163,19 +1190,25 @@
         <v>5</v>
       </c>
       <c r="AB12" s="3">
+        <v>116000</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD12" s="3">
         <v>107000</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AE12" s="3">
         <v>117000</v>
       </c>
-      <c r="AD12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG12" s="3">
         <v>113000</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1263,186 +1296,204 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="D14" s="3">
+        <v>44500</v>
+      </c>
+      <c r="E14" s="3">
+        <v>44500</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
         <v>116500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>116500</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3">
         <v>158500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>158500</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3">
         <v>112000</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
         <v>74000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>94000</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="3">
         <v>123000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>52000</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" s="3">
         <v>56000</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z14" s="3">
         <v>78000</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB14" s="3">
         <v>-30000</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD14" s="3">
         <v>14000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>-326000</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG14" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>93000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>93000</v>
+      </c>
+      <c r="F15" s="3">
         <v>136500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>136500</v>
       </c>
-      <c r="F15" s="3">
-        <v>128500</v>
-      </c>
-      <c r="G15" s="3">
-        <v>128500</v>
-      </c>
       <c r="H15" s="3">
+        <v>88000</v>
+      </c>
+      <c r="I15" s="3">
+        <v>88000</v>
+      </c>
+      <c r="J15" s="3">
         <v>136500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>136500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>74500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>74500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>143000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>143000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>70000</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R15" s="3">
         <v>151000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>83000</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U15" s="3">
         <v>100000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>61000</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X15" s="3">
         <v>56000</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z15" s="3">
         <v>57000</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB15" s="3">
         <v>127000</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD15" s="3">
         <v>65000</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE15" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1471,186 +1522,200 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1377500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1377500</v>
+      </c>
+      <c r="F17" s="3">
         <v>1266000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1266000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1212500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1212500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1249500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1249500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1174500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1174500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1229500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1229500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1096000</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R17" s="3">
         <v>2225000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2040000</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U17" s="3">
         <v>2257000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>2066000</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X17" s="3">
         <v>1973000</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z17" s="3">
         <v>2068000</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB17" s="3">
         <v>1909000</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD17" s="3">
         <v>1922000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>1571000</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG17" s="3">
         <v>1971000</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>224000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>224000</v>
+      </c>
+      <c r="F18" s="3">
         <v>214500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>214500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>279000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>279000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>164000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>164000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>233000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>233000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>137500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>137500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>211500</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R18" s="3">
         <v>300000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-5000</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U18" s="3">
         <v>396000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>419000</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X18" s="3">
         <v>491000</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z18" s="3">
         <v>372000</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB18" s="3">
         <v>520000</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD18" s="3">
         <v>414000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>770000</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG18" s="3">
         <v>357000</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1682,206 +1747,220 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-58000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-58000</v>
+      </c>
+      <c r="F20" s="3">
         <v>6500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>6500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>10000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>10000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>7000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>7000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>8000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>8000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>10000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>10000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>67000</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-29000</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U20" s="3">
         <v>-9000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-6000</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X20" s="3">
         <v>-51000</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-31000</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-24000</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-35000</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-30000</v>
       </c>
     </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>375000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>375000</v>
+      </c>
+      <c r="F21" s="3">
         <v>344500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>344500</v>
       </c>
-      <c r="F21" s="3">
-        <v>397500</v>
-      </c>
-      <c r="G21" s="3">
-        <v>397500</v>
-      </c>
       <c r="H21" s="3">
+        <v>357000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>357000</v>
+      </c>
+      <c r="J21" s="3">
         <v>293500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>293500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>299500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>299500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>270500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>270500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>214500</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R21" s="3">
         <v>842000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U21" s="3">
         <v>641000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>661000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X21" s="3">
         <v>647000</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z21" s="3">
         <v>569000</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB21" s="3">
         <v>724000</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="3">
         <v>630000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>984000</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG21" s="3">
         <v>541000</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E22" s="3">
+        <v>35500</v>
+      </c>
+      <c r="F22" s="3">
         <v>34500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>34500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>37500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>37500</v>
-      </c>
-      <c r="H22" s="3">
-        <v>35000</v>
-      </c>
-      <c r="I22" s="3">
-        <v>35000</v>
       </c>
       <c r="J22" s="3">
         <v>35000</v>
@@ -1890,38 +1969,38 @@
         <v>35000</v>
       </c>
       <c r="L22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="M22" s="3">
+        <v>35000</v>
+      </c>
+      <c r="N22" s="3">
         <v>31000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>31000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>22500</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>5</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U22" s="3">
         <v>27000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>30000</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W22" s="3" t="s">
         <v>5</v>
       </c>
@@ -1937,198 +2016,216 @@
       <c r="AA22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AB22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD22" s="3">
         <v>28000</v>
       </c>
-      <c r="AC22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD22" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE22" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG22" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>208500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>208500</v>
+      </c>
+      <c r="F23" s="3">
         <v>181000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>181000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>122500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>122500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>126500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>126500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>39500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>39500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>105500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>105500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>15500</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R23" s="3">
         <v>280000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-34000</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U23" s="3">
         <v>360000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>383000</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X23" s="3">
         <v>440000</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z23" s="3">
         <v>341000</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB23" s="3">
         <v>496000</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD23" s="3">
         <v>383000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>735000</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG23" s="3">
         <v>327000</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E24" s="3">
+        <v>42500</v>
+      </c>
+      <c r="F24" s="3">
         <v>34500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>34500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>23500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>23500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>19500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>19500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-6000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-6000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>19500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>19500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-7500</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R24" s="3">
         <v>-68000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-134000</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U24" s="3">
         <v>69000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>74000</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X24" s="3">
         <v>51000</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z24" s="3">
         <v>67000</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB24" s="3">
         <v>21000</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD24" s="3">
         <v>59000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>192000</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG24" s="3">
         <v>86000</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2216,186 +2313,204 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>166000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>166000</v>
+      </c>
+      <c r="F26" s="3">
         <v>146500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>146500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>99000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>99000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>107000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>107000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>45500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>45500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>86000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>86000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>23000</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R26" s="3">
         <v>348000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>100000</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U26" s="3">
         <v>291000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>309000</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X26" s="3">
         <v>389000</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z26" s="3">
         <v>274000</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB26" s="3">
         <v>475000</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD26" s="3">
         <v>324000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>543000</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG26" s="3">
         <v>241000</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>166000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>166000</v>
+      </c>
+      <c r="F27" s="3">
         <v>146500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>146500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>99000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>99000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>107000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>107000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>45500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>45500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>86000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>86000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>23000</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R27" s="3">
         <v>348000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>100000</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U27" s="3">
         <v>291000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>309000</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X27" s="3">
         <v>389000</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z27" s="3">
         <v>274000</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB27" s="3">
         <v>475000</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD27" s="3">
         <v>324000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>543000</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG27" s="3">
         <v>241000</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2483,8 +2598,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2536,33 +2657,33 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-32000</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2572,8 +2693,14 @@
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2661,8 +2788,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2750,186 +2883,204 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>58000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-6500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-6500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-10000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-10000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-7000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-7000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-8000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-8000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-10000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-10000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-67000</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>20000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>29000</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U32" s="3">
         <v>9000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>6000</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X32" s="3">
         <v>51000</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z32" s="3">
         <v>31000</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB32" s="3">
         <v>24000</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD32" s="3">
         <v>3000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>35000</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG32" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>166000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>166000</v>
+      </c>
+      <c r="F33" s="3">
         <v>146500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>146500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>99000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>99000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>107000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>107000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>45500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>45500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>86000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>86000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>23000</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R33" s="3">
         <v>348000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>100000</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U33" s="3">
         <v>291000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>309000</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X33" s="3">
         <v>389000</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z33" s="3">
         <v>274000</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB33" s="3">
         <v>443000</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD33" s="3">
         <v>324000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>543000</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG33" s="3">
         <v>241000</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3017,191 +3168,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>166000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>166000</v>
+      </c>
+      <c r="F35" s="3">
         <v>146500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>146500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>99000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>99000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>107000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>107000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>45500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>45500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>86000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>86000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>23000</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R35" s="3">
         <v>348000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>100000</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U35" s="3">
         <v>291000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>309000</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X35" s="3">
         <v>389000</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z35" s="3">
         <v>274000</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB35" s="3">
         <v>443000</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD35" s="3">
         <v>324000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>543000</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG35" s="3">
         <v>241000</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45836</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45744</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45472</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45380</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45108</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45017</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44289</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44009</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43918</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43645</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43554</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43372</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42917</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42735</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42644</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42553</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3233,8 +3402,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3266,97 +3437,105 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>557000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>557000</v>
+      </c>
+      <c r="F41" s="3">
         <v>676000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>676000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>619000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>619000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>568000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>568000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>302000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>302000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>190000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>190000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>350000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1762000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>347000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>277000</v>
-      </c>
-      <c r="R41" s="3">
-        <v>137000</v>
-      </c>
-      <c r="S41" s="3">
-        <v>365000</v>
       </c>
       <c r="T41" s="3">
         <v>137000</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>5</v>
+      <c r="U41" s="3">
+        <v>365000</v>
       </c>
       <c r="V41" s="3">
+        <v>137000</v>
+      </c>
+      <c r="W41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X41" s="3">
         <v>365000</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z41" s="3">
         <v>99000</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB41" s="3">
         <v>169000</v>
       </c>
-      <c r="AA41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD41" s="3">
         <v>69000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>100000</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG41" s="3">
         <v>85000</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3444,228 +3623,246 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1310000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1310000</v>
+      </c>
+      <c r="F43" s="3">
         <v>1484000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1484000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1241000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1241000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1399000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1399000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1214000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1214000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1277000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1277000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1178000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1211000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1231000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1328000</v>
-      </c>
-      <c r="R43" s="3">
-        <v>1280000</v>
-      </c>
-      <c r="S43" s="3">
-        <v>1317000</v>
       </c>
       <c r="T43" s="3">
         <v>1280000</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>5</v>
+      <c r="U43" s="3">
+        <v>1317000</v>
       </c>
       <c r="V43" s="3">
+        <v>1280000</v>
+      </c>
+      <c r="W43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X43" s="3">
         <v>1317000</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z43" s="3">
         <v>1205000</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB43" s="3">
         <v>1258000</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD43" s="3">
         <v>1212000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>1185000</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG43" s="3">
         <v>1166000</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2117000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>2117000</v>
+      </c>
+      <c r="F44" s="3">
         <v>2467000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>2467000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>2387000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>2387000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>2491000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>2491000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>2395000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>2395000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>2411000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>2411000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>2205000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>1691000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>1721000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>1614000</v>
-      </c>
-      <c r="R44" s="3">
-        <v>1532000</v>
-      </c>
-      <c r="S44" s="3">
-        <v>1395000</v>
       </c>
       <c r="T44" s="3">
         <v>1532000</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>5</v>
+      <c r="U44" s="3">
+        <v>1395000</v>
       </c>
       <c r="V44" s="3">
+        <v>1532000</v>
+      </c>
+      <c r="W44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X44" s="3">
         <v>1395000</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z44" s="3">
         <v>1352000</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB44" s="3">
         <v>1304000</v>
       </c>
-      <c r="AA44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD44" s="3">
         <v>1298000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>1244000</v>
       </c>
-      <c r="AD44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG44" s="3">
         <v>1291000</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F45" s="3">
+      <c r="D45" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>20000</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3">
         <v>47000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>47000</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L45" s="3">
         <v>27000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>27000</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P45" s="3">
         <v>47000</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
@@ -3702,126 +3899,138 @@
       <c r="AB45" s="3">
         <v>0</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE45" s="3">
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG45" s="3">
         <v>10000</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4103000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>4103000</v>
+      </c>
+      <c r="F46" s="3">
         <v>4627000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>4627000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>4421000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>4421000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>4458000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>4458000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>4030000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>4030000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>3878000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>3878000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>3856000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>4664000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>3299000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>3219000</v>
-      </c>
-      <c r="R46" s="3">
-        <v>2949000</v>
-      </c>
-      <c r="S46" s="3">
-        <v>3077000</v>
       </c>
       <c r="T46" s="3">
         <v>2949000</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>5</v>
+      <c r="U46" s="3">
+        <v>3077000</v>
       </c>
       <c r="V46" s="3">
+        <v>2949000</v>
+      </c>
+      <c r="W46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X46" s="3">
         <v>3077000</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z46" s="3">
         <v>2656000</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB46" s="3">
         <v>2731000</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD46" s="3">
         <v>2579000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>2529000</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG46" s="3">
         <v>2552000</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>151000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>151000</v>
+      </c>
+      <c r="F47" s="3">
         <v>36000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>36000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>16000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>16000</v>
-      </c>
-      <c r="H47" s="3">
-        <v>24000</v>
-      </c>
-      <c r="I47" s="3">
-        <v>24000</v>
       </c>
       <c r="J47" s="3">
         <v>24000</v>
@@ -3830,245 +4039,263 @@
         <v>24000</v>
       </c>
       <c r="L47" s="3">
+        <v>24000</v>
+      </c>
+      <c r="M47" s="3">
+        <v>24000</v>
+      </c>
+      <c r="N47" s="3">
         <v>35000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>35000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>58000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>117000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>106000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>110000</v>
-      </c>
-      <c r="R47" s="3">
-        <v>109000</v>
-      </c>
-      <c r="S47" s="3">
-        <v>139000</v>
       </c>
       <c r="T47" s="3">
         <v>109000</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>5</v>
+      <c r="U47" s="3">
+        <v>139000</v>
       </c>
       <c r="V47" s="3">
+        <v>109000</v>
+      </c>
+      <c r="W47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X47" s="3">
         <v>139000</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z47" s="3">
         <v>140000</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB47" s="3">
         <v>139000</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD47" s="3">
         <v>135000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>137000</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG47" s="3">
         <v>127000</v>
       </c>
     </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1638000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1638000</v>
+      </c>
+      <c r="F48" s="3">
         <v>1436000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1436000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1422000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1422000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1441000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1441000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1470000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1470000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1421000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1421000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1455000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1449000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1353000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1323000</v>
-      </c>
-      <c r="R48" s="3">
-        <v>1226000</v>
-      </c>
-      <c r="S48" s="3">
-        <v>1062000</v>
       </c>
       <c r="T48" s="3">
         <v>1226000</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>5</v>
+      <c r="U48" s="3">
+        <v>1062000</v>
       </c>
       <c r="V48" s="3">
+        <v>1226000</v>
+      </c>
+      <c r="W48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X48" s="3">
         <v>1062000</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z48" s="3">
         <v>1056000</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB48" s="3">
         <v>1049000</v>
       </c>
-      <c r="AA48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD48" s="3">
         <v>1032000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>982000</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG48" s="3">
         <v>946000</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3990000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>3990000</v>
+      </c>
+      <c r="F49" s="3">
         <v>4073000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>4073000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>4058000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>4058000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>4216000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>4216000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>4102000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>4102000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>4229000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>4229000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>4267000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>4414000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>4398000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>4356000</v>
-      </c>
-      <c r="R49" s="3">
-        <v>4391000</v>
-      </c>
-      <c r="S49" s="3">
-        <v>3547000</v>
       </c>
       <c r="T49" s="3">
         <v>4391000</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>5</v>
+      <c r="U49" s="3">
+        <v>3547000</v>
       </c>
       <c r="V49" s="3">
+        <v>4391000</v>
+      </c>
+      <c r="W49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X49" s="3">
         <v>3547000</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z49" s="3">
         <v>3638000</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB49" s="3">
         <v>3742000</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD49" s="3">
         <v>3587000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>3599000</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG49" s="3">
         <v>3762000</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4156,8 +4383,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4245,97 +4478,109 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>228000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>228000</v>
+      </c>
+      <c r="F52" s="3">
         <v>119000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>119000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>87000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>87000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>84000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>84000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>87000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>87000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>93000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>93000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>153000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>368000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>383000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>291000</v>
-      </c>
-      <c r="R52" s="3">
-        <v>271000</v>
-      </c>
-      <c r="S52" s="3">
-        <v>234000</v>
       </c>
       <c r="T52" s="3">
         <v>271000</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>5</v>
+      <c r="U52" s="3">
+        <v>234000</v>
       </c>
       <c r="V52" s="3">
+        <v>271000</v>
+      </c>
+      <c r="W52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X52" s="3">
         <v>234000</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z52" s="3">
         <v>223000</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB52" s="3">
         <v>205000</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD52" s="3">
         <v>106000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>97000</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG52" s="3">
         <v>115000</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4423,97 +4668,109 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10457000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>10457000</v>
+      </c>
+      <c r="F54" s="3">
         <v>10692000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>10692000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>10354000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>10354000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>10542000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>10542000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>9987000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>9987000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>9844000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>9844000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>9966000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>11012000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>9539000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>9299000</v>
-      </c>
-      <c r="R54" s="3">
-        <v>8946000</v>
-      </c>
-      <c r="S54" s="3">
-        <v>8059000</v>
       </c>
       <c r="T54" s="3">
         <v>8946000</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>5</v>
+      <c r="U54" s="3">
+        <v>8059000</v>
       </c>
       <c r="V54" s="3">
+        <v>8946000</v>
+      </c>
+      <c r="W54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X54" s="3">
         <v>8059000</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z54" s="3">
         <v>7713000</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB54" s="3">
         <v>7866000</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD54" s="3">
         <v>7439000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>7344000</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG54" s="3">
         <v>7502000</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4545,8 +4802,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4578,461 +4837,493 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1160000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1160000</v>
+      </c>
+      <c r="F57" s="3">
         <v>1097000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1097000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1082000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1082000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1024000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1024000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1016000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1016000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>955000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>955000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1029000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1022000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>875000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1046000</v>
-      </c>
-      <c r="R57" s="3">
-        <v>906000</v>
-      </c>
-      <c r="S57" s="3">
-        <v>957000</v>
       </c>
       <c r="T57" s="3">
         <v>906000</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>5</v>
+      <c r="U57" s="3">
+        <v>957000</v>
       </c>
       <c r="V57" s="3">
+        <v>906000</v>
+      </c>
+      <c r="W57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X57" s="3">
         <v>957000</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z57" s="3">
         <v>831000</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB57" s="3">
         <v>957000</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD57" s="3">
         <v>792000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>884000</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG57" s="3">
         <v>842000</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>150000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>150000</v>
+      </c>
+      <c r="F58" s="3">
         <v>157000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>157000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>63000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>63000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>380000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>380000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>765000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>765000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>407000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>407000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>160000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>337000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>163000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>72000</v>
-      </c>
-      <c r="R58" s="3">
-        <v>199000</v>
-      </c>
-      <c r="S58" s="3">
-        <v>164000</v>
       </c>
       <c r="T58" s="3">
         <v>199000</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>5</v>
+      <c r="U58" s="3">
+        <v>164000</v>
       </c>
       <c r="V58" s="3">
+        <v>199000</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X58" s="3">
         <v>164000</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z58" s="3">
         <v>86000</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB58" s="3">
         <v>27000</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD58" s="3">
         <v>64000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>86000</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG58" s="3">
         <v>71000</v>
       </c>
     </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>285000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>285000</v>
+      </c>
+      <c r="F59" s="3">
         <v>287000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>287000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>386000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>386000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>373000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>373000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>490000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>490000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>405000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>405000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>526000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>329000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>478000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>446000</v>
-      </c>
-      <c r="R59" s="3">
-        <v>369000</v>
-      </c>
-      <c r="S59" s="3">
-        <v>344000</v>
       </c>
       <c r="T59" s="3">
         <v>369000</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>5</v>
+      <c r="U59" s="3">
+        <v>344000</v>
       </c>
       <c r="V59" s="3">
+        <v>369000</v>
+      </c>
+      <c r="W59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X59" s="3">
         <v>344000</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z59" s="3">
         <v>330000</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB59" s="3">
         <v>362000</v>
       </c>
-      <c r="AA59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD59" s="3">
         <v>329000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>378000</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG59" s="3">
         <v>432000</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1595000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1595000</v>
+      </c>
+      <c r="F60" s="3">
         <v>1541000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1541000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1531000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1531000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1777000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1777000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2271000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2271000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1767000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1767000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1715000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1688000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1516000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1564000</v>
-      </c>
-      <c r="R60" s="3">
-        <v>1474000</v>
-      </c>
-      <c r="S60" s="3">
-        <v>1465000</v>
       </c>
       <c r="T60" s="3">
         <v>1474000</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>5</v>
+      <c r="U60" s="3">
+        <v>1465000</v>
       </c>
       <c r="V60" s="3">
+        <v>1474000</v>
+      </c>
+      <c r="W60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X60" s="3">
         <v>1465000</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z60" s="3">
         <v>1247000</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB60" s="3">
         <v>1346000</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD60" s="3">
         <v>1185000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>1348000</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG60" s="3">
         <v>1345000</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3177000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>3177000</v>
+      </c>
+      <c r="F61" s="3">
         <v>3297000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>3297000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>3258000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>3258000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>3275000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>3275000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>2319000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>2319000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2633000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>2633000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>2712000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>3353000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>2476000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1975000</v>
-      </c>
-      <c r="R61" s="3">
-        <v>1980000</v>
-      </c>
-      <c r="S61" s="3">
-        <v>1301000</v>
       </c>
       <c r="T61" s="3">
         <v>1980000</v>
       </c>
       <c r="U61" s="3">
-        <v>0</v>
+        <v>1301000</v>
       </c>
       <c r="V61" s="3">
+        <v>1980000</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>1301000</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>1420000</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>1423000</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>1604000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>1564000</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
         <v>1708000</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>190000</v>
+        <v>272000</v>
       </c>
       <c r="E62" s="3">
-        <v>190000</v>
+        <v>272000</v>
       </c>
       <c r="F62" s="3">
         <v>190000</v>
@@ -5041,79 +5332,85 @@
         <v>190000</v>
       </c>
       <c r="H62" s="3">
+        <v>190000</v>
+      </c>
+      <c r="I62" s="3">
+        <v>190000</v>
+      </c>
+      <c r="J62" s="3">
         <v>167000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>167000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>83000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>83000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>137000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>137000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>174000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>692000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>587000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>619000</v>
-      </c>
-      <c r="R62" s="3">
-        <v>540000</v>
-      </c>
-      <c r="S62" s="3">
-        <v>419000</v>
       </c>
       <c r="T62" s="3">
         <v>540000</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>5</v>
+      <c r="U62" s="3">
+        <v>419000</v>
       </c>
       <c r="V62" s="3">
+        <v>540000</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X62" s="3">
         <v>419000</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z62" s="3">
         <v>403000</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB62" s="3">
         <v>453000</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD62" s="3">
         <v>449000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>474000</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG62" s="3">
         <v>505000</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5201,8 +5498,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5290,8 +5593,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5379,97 +5688,109 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5168000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>5168000</v>
+      </c>
+      <c r="F66" s="3">
         <v>5156000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>5156000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>5089000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>5089000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>5337000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>5337000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>4770000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>4770000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>4611000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>4611000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>4707000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>5733000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>4579000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>4158000</v>
-      </c>
-      <c r="R66" s="3">
-        <v>3994000</v>
-      </c>
-      <c r="S66" s="3">
-        <v>3185000</v>
       </c>
       <c r="T66" s="3">
         <v>3994000</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>5</v>
+      <c r="U66" s="3">
+        <v>3185000</v>
       </c>
       <c r="V66" s="3">
+        <v>3994000</v>
+      </c>
+      <c r="W66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X66" s="3">
         <v>3185000</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z66" s="3">
         <v>3070000</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB66" s="3">
         <v>3222000</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD66" s="3">
         <v>3238000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>3386000</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG66" s="3">
         <v>3558000</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5501,8 +5822,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5590,8 +5913,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5679,8 +6008,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5768,8 +6103,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5857,97 +6198,109 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5323000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>5323000</v>
+      </c>
+      <c r="F72" s="3">
         <v>5121000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>5121000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>5018000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>5018000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>4934000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>4934000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>4906000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>4906000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>4963000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>4963000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>5026000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>4647000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>4349000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>4543000</v>
-      </c>
-      <c r="R72" s="3">
-        <v>4370000</v>
-      </c>
-      <c r="S72" s="3">
-        <v>4303000</v>
       </c>
       <c r="T72" s="3">
         <v>4370000</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>5</v>
+      <c r="U72" s="3">
+        <v>4303000</v>
       </c>
       <c r="V72" s="3">
+        <v>4370000</v>
+      </c>
+      <c r="W72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X72" s="3">
         <v>4303000</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z72" s="3">
         <v>4092000</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB72" s="3">
         <v>4118000</v>
       </c>
-      <c r="AA72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD72" s="3">
         <v>3680000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>3610000</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG72" s="3">
         <v>3450000</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6035,8 +6388,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6124,8 +6483,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6213,97 +6578,109 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5289000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>5289000</v>
+      </c>
+      <c r="F76" s="3">
         <v>5536000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>5536000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>5265000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>5265000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>5205000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>5205000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>5217000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>5217000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>5233000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>5233000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>5259000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>5279000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>4960000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>5141000</v>
-      </c>
-      <c r="R76" s="3">
-        <v>4952000</v>
-      </c>
-      <c r="S76" s="3">
-        <v>4874000</v>
       </c>
       <c r="T76" s="3">
         <v>4952000</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>5</v>
+      <c r="U76" s="3">
+        <v>4874000</v>
       </c>
       <c r="V76" s="3">
+        <v>4952000</v>
+      </c>
+      <c r="W76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X76" s="3">
         <v>4874000</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z76" s="3">
         <v>4643000</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB76" s="3">
         <v>4644000</v>
       </c>
-      <c r="AA76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD76" s="3">
         <v>4201000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>3958000</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG76" s="3">
         <v>3944000</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6391,191 +6768,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45836</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45744</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45472</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45380</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45108</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45017</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44289</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44009</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43918</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43645</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43554</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43372</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42917</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42735</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42644</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42553</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>166000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>166000</v>
+      </c>
+      <c r="F81" s="3">
         <v>146500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>146500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>99000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>99000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>107000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>107000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>45500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>45500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>86000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>86000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>23000</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R81" s="3">
         <v>348000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>100000</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U81" s="3">
         <v>291000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>309000</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X81" s="3">
         <v>389000</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z81" s="3">
         <v>274000</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB81" s="3">
         <v>443000</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD81" s="3">
         <v>324000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>543000</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG81" s="3">
         <v>241000</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6607,73 +7002,75 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>69500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>69500</v>
+      </c>
+      <c r="F83" s="3">
         <v>93000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>93000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>61000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>61000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>92000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>92000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>57500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>57500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>102000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>102000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>59000</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R83" s="3">
         <v>562000</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U83" s="3">
         <v>254000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>248000</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X83" s="3">
         <v>207000</v>
-      </c>
-      <c r="W83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X83" s="3">
-        <v>228000</v>
       </c>
       <c r="Y83" s="3" t="s">
         <v>5</v>
@@ -6685,19 +7082,25 @@
         <v>5</v>
       </c>
       <c r="AB83" s="3">
+        <v>228000</v>
+      </c>
+      <c r="AC83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD83" s="3">
         <v>219000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>249000</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG83" s="3">
         <v>214000</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6785,8 +7188,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6874,8 +7283,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6963,8 +7378,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7052,8 +7473,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7141,97 +7568,109 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>444500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>444500</v>
+      </c>
+      <c r="F89" s="3">
         <v>198000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>198000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>374500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>374500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>119000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>119000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>247500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>247500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>56500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>56500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>130500</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R89" s="3">
         <v>935000</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U89" s="3">
         <v>717000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>451000</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X89" s="3">
         <v>634000</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z89" s="3">
         <v>297000</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB89" s="3">
         <v>739000</v>
       </c>
-      <c r="AA89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD89" s="3">
         <v>351000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>580000</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG89" s="3">
         <v>269000</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7263,97 +7702,105 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-147000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-147000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-69500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-69500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-104500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-104500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-86000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-86000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-130000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-130000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-83500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-83500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-92500</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-255000</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-188000</v>
       </c>
       <c r="Q91" s="3">
         <v>-255000</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>5</v>
+      <c r="R91" s="3">
+        <v>-188000</v>
       </c>
       <c r="S91" s="3">
         <v>-255000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="T91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U91" s="3">
+        <v>-255000</v>
+      </c>
+      <c r="V91" s="3">
         <v>-153000</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X91" s="3">
         <v>-169000</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-178000</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-198000</v>
       </c>
-      <c r="AA91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-178000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-218000</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-174000</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7441,8 +7888,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7530,97 +7983,109 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-135500</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-135500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-67500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-67500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-104500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-104500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-180000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-180000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-133000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-133000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-91000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-91000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-102000</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R94" s="3">
         <v>-606000</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U94" s="3">
         <v>-286000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-965000</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X94" s="3">
         <v>-179000</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z94" s="3">
         <v>-199000</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB94" s="3">
         <v>-326000</v>
       </c>
-      <c r="AA94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD94" s="3">
         <v>-217000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>5000</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-388000</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7652,97 +8117,105 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>64000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>64000</v>
+      </c>
+      <c r="F96" s="3">
         <v>101000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>101000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>62500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>62500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>101000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>101000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>63000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>63000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>100500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>100500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>62500</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-328000</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-126000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-192000</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-123000</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-198000</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-107000</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-162000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-109000</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-170000</v>
       </c>
     </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7830,8 +8303,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7919,8 +8398,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8008,168 +8493,180 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-369000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-369000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-108500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-108500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-229000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-229000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>186000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>186000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-57000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-57000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-43000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-43000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-111000</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R100" s="3">
         <v>1164000</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U100" s="3">
         <v>-296000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>303000</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X100" s="3">
         <v>-202000</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-169000</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-304000</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-130000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-598000</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG100" s="3">
         <v>69000</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-2500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-2500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>1000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-3000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-3000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-1500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-1500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-4000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-4000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-2500</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R101" s="3">
         <v>1000</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
-      <c r="U101" s="3" t="s">
-        <v>5</v>
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
       </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X101" s="3">
         <v>-1000</v>
       </c>
-      <c r="W101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-3000</v>
-      </c>
-      <c r="Y101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>2000</v>
       </c>
       <c r="AA101" s="3" t="s">
         <v>5</v>
@@ -8177,102 +8674,114 @@
       <c r="AB101" s="3">
         <v>2000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AC101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="AE101" s="3">
         <v>-2000</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-60000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-60000</v>
+      </c>
+      <c r="F102" s="3">
         <v>28000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>28000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>36000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>36000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>122500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>122500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>58500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>58500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-80500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-80500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-84000</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R102" s="3">
         <v>1494000</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U102" s="3">
         <v>135000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-211000</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X102" s="3">
         <v>252000</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z102" s="3">
         <v>-74000</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB102" s="3">
         <v>111000</v>
       </c>
-      <c r="AA102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD102" s="3">
         <v>6000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-15000</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG102" s="3">
         <v>-49000</v>
       </c>
     </row>
